--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/X13.cis.beta.carotene/RANDOMSEARCH_DETAILS_X13.cis.beta.carotene.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/X13.cis.beta.carotene/RANDOMSEARCH_DETAILS_X13.cis.beta.carotene.xlsx
@@ -469,17 +469,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9301</v>
+        <v>0.9308</v>
       </c>
       <c r="F2" t="n">
-        <v>15.3604</v>
+        <v>15.331</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>27.4919</v>
       </c>
     </row>
     <row r="3">
@@ -498,17 +498,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.968</v>
+        <v>0.9676</v>
       </c>
       <c r="F3" t="n">
-        <v>11.2597</v>
+        <v>11.2858</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>26.6443</v>
       </c>
     </row>
     <row r="4">
@@ -527,17 +527,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9381</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>14.3493</v>
+        <v>14.3543</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>27.5826</v>
       </c>
     </row>
     <row r="5">
@@ -556,17 +556,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.7892</v>
+        <v>0.7895</v>
       </c>
       <c r="F5" t="n">
-        <v>24.8317</v>
+        <v>24.8281</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>35.3411</v>
       </c>
     </row>
     <row r="6">
@@ -585,17 +585,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.7755</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>25.214</v>
+        <v>25.2078</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>35.6516</v>
       </c>
     </row>
     <row r="7">
@@ -614,17 +614,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.8902</v>
+        <v>0.8905</v>
       </c>
       <c r="F7" t="n">
-        <v>18.1835</v>
+        <v>18.17</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>28.5111</v>
       </c>
     </row>
     <row r="8">
@@ -643,17 +643,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.8552999999999999</v>
+        <v>0.8551</v>
       </c>
       <c r="F8" t="n">
-        <v>20.0931</v>
+        <v>20.1</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>29.54</v>
       </c>
     </row>
     <row r="9">
@@ -672,17 +672,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.9306</v>
+        <v>0.9645</v>
       </c>
       <c r="F9" t="n">
-        <v>15.1421</v>
+        <v>11.6891</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>26.929</v>
       </c>
     </row>
     <row r="10">
@@ -701,17 +701,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.8575</v>
+        <v>0.8574000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>19.9812</v>
+        <v>19.9878</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>29.5095</v>
       </c>
     </row>
     <row r="11">
@@ -730,17 +730,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.8574000000000001</v>
+        <v>0.8571</v>
       </c>
       <c r="F11" t="n">
-        <v>19.9782</v>
+        <v>19.9889</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>29.4708</v>
       </c>
     </row>
     <row r="12">
@@ -759,17 +759,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>0.8569</v>
       </c>
       <c r="F12" t="n">
-        <v>20.0034</v>
+        <v>19.9988</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>29.5153</v>
       </c>
     </row>
     <row r="13">
@@ -788,17 +788,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.857</v>
+        <v>0.8568</v>
       </c>
       <c r="F13" t="n">
-        <v>19.9973</v>
+        <v>20.0011</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>29.498</v>
       </c>
     </row>
     <row r="14">
@@ -817,17 +817,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.8576</v>
+        <v>0.8572</v>
       </c>
       <c r="F14" t="n">
-        <v>19.9804</v>
+        <v>19.9931</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>29.4698</v>
       </c>
     </row>
     <row r="15">
@@ -846,17 +846,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.8573</v>
+        <v>0.8572</v>
       </c>
       <c r="F15" t="n">
-        <v>19.9886</v>
+        <v>19.9851</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>29.4889</v>
       </c>
     </row>
     <row r="16">
@@ -875,17 +875,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.8578</v>
+        <v>0.8577</v>
       </c>
       <c r="F16" t="n">
-        <v>19.9552</v>
+        <v>19.9568</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>29.4599</v>
       </c>
     </row>
     <row r="17">
@@ -904,17 +904,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.857</v>
+        <v>0.8569</v>
       </c>
       <c r="F17" t="n">
-        <v>20.0071</v>
+        <v>20.005</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>29.4787</v>
       </c>
     </row>
     <row r="18">
@@ -933,17 +933,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.8941</v>
+        <v>0.894</v>
       </c>
       <c r="F18" t="n">
-        <v>17.9858</v>
+        <v>17.9892</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>28.1301</v>
       </c>
     </row>
     <row r="19">
@@ -962,17 +962,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9577</v>
+        <v>0.8925999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>12.2014</v>
+        <v>18.0138</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>28.4087</v>
       </c>
     </row>
     <row r="20">
@@ -991,17 +991,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.8875</v>
+        <v>0.8877</v>
       </c>
       <c r="F20" t="n">
-        <v>18.2758</v>
+        <v>18.2639</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>28.3009</v>
       </c>
     </row>
     <row r="21">
@@ -1020,17 +1020,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.8866000000000001</v>
+        <v>0.8865</v>
       </c>
       <c r="F21" t="n">
-        <v>18.3301</v>
+        <v>18.3379</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>28.6499</v>
       </c>
     </row>
     <row r="22">
@@ -1049,17 +1049,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E22" t="n">
         <v>0.8837</v>
       </c>
       <c r="F22" t="n">
-        <v>18.477</v>
+        <v>18.4765</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>28.6816</v>
       </c>
     </row>
     <row r="23">
@@ -1078,17 +1078,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.8849</v>
+        <v>0.885</v>
       </c>
       <c r="F23" t="n">
-        <v>18.4208</v>
+        <v>18.4164</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>28.8859</v>
       </c>
     </row>
     <row r="24">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.9464</v>
+        <v>0.9458</v>
       </c>
       <c r="F24" t="n">
-        <v>13.3886</v>
+        <v>13.4048</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>28.8134</v>
       </c>
     </row>
     <row r="25">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E25" t="n">
         <v>0.8663999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>19.4575</v>
+        <v>19.4528</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>28.8812</v>
       </c>
     </row>
     <row r="26">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.9446</v>
+        <v>0.944</v>
       </c>
       <c r="F26" t="n">
-        <v>13.7302</v>
+        <v>13.7728</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>28.2209</v>
       </c>
     </row>
     <row r="27">
@@ -1194,17 +1194,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9774</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>10.0371</v>
+        <v>10</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>28.1644</v>
       </c>
     </row>
     <row r="28">
@@ -1223,17 +1223,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.9745</v>
+        <v>0.8945</v>
       </c>
       <c r="F28" t="n">
-        <v>10.4681</v>
+        <v>17.9028</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>28.2046</v>
       </c>
     </row>
     <row r="29">
@@ -1252,17 +1252,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.8783</v>
+        <v>0.9761</v>
       </c>
       <c r="F29" t="n">
-        <v>18.9194</v>
+        <v>10.0244</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>27.9714</v>
       </c>
     </row>
     <row r="30">
@@ -1281,17 +1281,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.8754</v>
+        <v>0.8753</v>
       </c>
       <c r="F30" t="n">
-        <v>19.0202</v>
+        <v>19.0231</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>28.3479</v>
       </c>
     </row>
     <row r="31">
@@ -1310,17 +1310,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E31" t="n">
         <v>0.8833</v>
       </c>
       <c r="F31" t="n">
-        <v>18.5422</v>
+        <v>18.5399</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>28.6398</v>
       </c>
     </row>
     <row r="32">
@@ -1339,17 +1339,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.8879</v>
+        <v>0.8878</v>
       </c>
       <c r="F32" t="n">
-        <v>18.2466</v>
+        <v>18.2471</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>28.6868</v>
       </c>
     </row>
     <row r="33">
@@ -1368,17 +1368,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.9736</v>
+        <v>0.9732</v>
       </c>
       <c r="F33" t="n">
-        <v>10.5842</v>
+        <v>10.6212</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>28.6509</v>
       </c>
     </row>
     <row r="34">
@@ -1397,17 +1397,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9673</v>
+        <v>0.9398</v>
       </c>
       <c r="F34" t="n">
-        <v>11.016</v>
+        <v>13.8267</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>27.1181</v>
       </c>
     </row>
     <row r="35">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E35" t="n">
         <v>0.9389999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>13.8962</v>
+        <v>13.8858</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>27.1855</v>
       </c>
     </row>
     <row r="36">
@@ -1455,17 +1455,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.9036999999999999</v>
+        <v>0.915</v>
       </c>
       <c r="F36" t="n">
-        <v>17.9255</v>
+        <v>17.0506</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>27.3222</v>
       </c>
     </row>
     <row r="37">
@@ -1484,17 +1484,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E37" t="n">
         <v>0.9133</v>
       </c>
       <c r="F37" t="n">
-        <v>17.0002</v>
+        <v>17</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>27.2485</v>
       </c>
     </row>
     <row r="38">
@@ -1513,17 +1513,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.907</v>
+        <v>0.9069</v>
       </c>
       <c r="F38" t="n">
-        <v>17.3613</v>
+        <v>17.3628</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>27.4442</v>
       </c>
     </row>
     <row r="39">
@@ -1542,17 +1542,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.8901</v>
+        <v>0.89</v>
       </c>
       <c r="F39" t="n">
-        <v>18.4534</v>
+        <v>18.4554</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>27.8853</v>
       </c>
     </row>
     <row r="40">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E40" t="n">
         <v>0.9055</v>
       </c>
       <c r="F40" t="n">
-        <v>17.2372</v>
+        <v>17.2383</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>27.6123</v>
       </c>
     </row>
     <row r="41">
@@ -1600,17 +1600,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.9671</v>
+        <v>0.9403</v>
       </c>
       <c r="F41" t="n">
-        <v>11.0402</v>
+        <v>13.811</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>27.0709</v>
       </c>
     </row>
     <row r="42">
@@ -1629,17 +1629,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.9389</v>
       </c>
       <c r="F42" t="n">
-        <v>13.8947</v>
+        <v>13.8869</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>27.1259</v>
       </c>
     </row>
     <row r="43">
@@ -1658,17 +1658,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.9155</v>
+        <v>0.9249000000000001</v>
       </c>
       <c r="F43" t="n">
-        <v>17.0201</v>
+        <v>15.4552</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>27.2956</v>
       </c>
     </row>
     <row r="44">
@@ -1687,17 +1687,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E44" t="n">
         <v>0.9135</v>
       </c>
       <c r="F44" t="n">
-        <v>16.9997</v>
+        <v>16.9971</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>27.1713</v>
       </c>
     </row>
     <row r="45">
@@ -1716,17 +1716,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.9211</v>
+        <v>0.9078000000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>16.2064</v>
+        <v>17.3075</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>27.3845</v>
       </c>
     </row>
     <row r="46">
@@ -1745,17 +1745,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.8911</v>
+        <v>0.9157</v>
       </c>
       <c r="F46" t="n">
-        <v>18.431</v>
+        <v>16.5345</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>27.7367</v>
       </c>
     </row>
     <row r="47">
@@ -1774,17 +1774,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.8888</v>
+        <v>0.8887</v>
       </c>
       <c r="F47" t="n">
-        <v>18.4416</v>
+        <v>18.4461</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>27.6215</v>
       </c>
     </row>
     <row r="48">
@@ -1803,17 +1803,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E48" t="n">
         <v>0.9159</v>
       </c>
       <c r="F48" t="n">
-        <v>16.8845</v>
+        <v>16.8735</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>27.0833</v>
       </c>
     </row>
     <row r="49">
@@ -1832,17 +1832,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.9311</v>
+        <v>0.9305</v>
       </c>
       <c r="F49" t="n">
-        <v>14.8756</v>
+        <v>14.9283</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>26.9496</v>
       </c>
     </row>
     <row r="50">
@@ -1861,17 +1861,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.9024</v>
+        <v>0.9028</v>
       </c>
       <c r="F50" t="n">
-        <v>19.7813</v>
+        <v>19.7618</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>33.8379</v>
       </c>
     </row>
     <row r="51">
@@ -1890,17 +1890,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.833</v>
+        <v>0.8331</v>
       </c>
       <c r="F51" t="n">
-        <v>23.4716</v>
+        <v>23.4596</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>34.634</v>
       </c>
     </row>
     <row r="52">
@@ -1919,17 +1919,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.8335</v>
+        <v>0.8336</v>
       </c>
       <c r="F52" t="n">
-        <v>23.4374</v>
+        <v>23.4385</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>34.5121</v>
       </c>
     </row>
     <row r="53">
@@ -1948,17 +1948,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E53" t="n">
         <v>0.8502999999999999</v>
       </c>
       <c r="F53" t="n">
-        <v>22.7632</v>
+        <v>22.7599</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>33.8948</v>
       </c>
     </row>
     <row r="54">
@@ -1977,17 +1977,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.8737</v>
+        <v>0.8739</v>
       </c>
       <c r="F54" t="n">
-        <v>20.7489</v>
+        <v>20.7312</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>33.5407</v>
       </c>
     </row>
     <row r="55">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.8586</v>
+        <v>0.8587</v>
       </c>
       <c r="F55" t="n">
-        <v>21.8533</v>
+        <v>21.848</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>34.4035</v>
       </c>
     </row>
     <row r="56">
@@ -2035,17 +2035,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.9012</v>
+        <v>0.9011</v>
       </c>
       <c r="F56" t="n">
-        <v>19.2472</v>
+        <v>19.2681</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>33.6129</v>
       </c>
     </row>
     <row r="57">
@@ -2064,17 +2064,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.8489</v>
+        <v>0.8488</v>
       </c>
       <c r="F57" t="n">
-        <v>22.6711</v>
+        <v>22.6746</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>34.0693</v>
       </c>
     </row>
     <row r="58">
@@ -2093,17 +2093,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.7768</v>
+        <v>0.7772</v>
       </c>
       <c r="F58" t="n">
-        <v>25.1839</v>
+        <v>25.173</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>35.6617</v>
       </c>
     </row>
     <row r="59">
@@ -2122,17 +2122,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.7772</v>
+        <v>0.7774</v>
       </c>
       <c r="F59" t="n">
-        <v>25.1695</v>
+        <v>25.1655</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>35.6385</v>
       </c>
     </row>
     <row r="60">
@@ -2151,17 +2151,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.7773</v>
+        <v>0.7776</v>
       </c>
       <c r="F60" t="n">
-        <v>25.157</v>
+        <v>25.1502</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>35.6239</v>
       </c>
     </row>
     <row r="61">
@@ -2180,17 +2180,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.7785</v>
+        <v>0.7786999999999999</v>
       </c>
       <c r="F61" t="n">
-        <v>25.1124</v>
+        <v>25.1075</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>35.6471</v>
       </c>
     </row>
     <row r="62">
@@ -2209,17 +2209,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E62" t="n">
         <v>0.8122</v>
       </c>
       <c r="F62" t="n">
-        <v>23.9443</v>
+        <v>23.9425</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>35.7992</v>
       </c>
     </row>
     <row r="63">
@@ -2238,17 +2238,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.8169</v>
+        <v>0.8168</v>
       </c>
       <c r="F63" t="n">
-        <v>23.709</v>
+        <v>23.7081</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>35.7762</v>
       </c>
     </row>
     <row r="64">
@@ -2267,17 +2267,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8649</v>
       </c>
       <c r="F64" t="n">
-        <v>23.8769</v>
+        <v>21.5597</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>35.8058</v>
       </c>
     </row>
     <row r="65">
@@ -2296,17 +2296,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.864</v>
+        <v>0.8635</v>
       </c>
       <c r="F65" t="n">
-        <v>21.5622</v>
+        <v>21.5804</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>35.7921</v>
       </c>
     </row>
     <row r="66">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.9384</v>
+        <v>0.9583</v>
       </c>
       <c r="F66" t="n">
-        <v>16.1004</v>
+        <v>14.4913</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>33.9232</v>
       </c>
     </row>
     <row r="67">
@@ -2354,17 +2354,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.8855</v>
+        <v>0.8854</v>
       </c>
       <c r="F67" t="n">
-        <v>20.3068</v>
+        <v>20.3074</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>33.9311</v>
       </c>
     </row>
     <row r="68">
@@ -2383,17 +2383,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E68" t="n">
         <v>0.8645</v>
       </c>
       <c r="F68" t="n">
-        <v>21.7716</v>
+        <v>21.7712</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>33.9799</v>
       </c>
     </row>
     <row r="69">
@@ -2412,17 +2412,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.9439</v>
+        <v>0.9429</v>
       </c>
       <c r="F69" t="n">
-        <v>13.7834</v>
+        <v>13.8199</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>28.5488</v>
       </c>
     </row>
     <row r="70">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.9433</v>
+        <v>0.9358</v>
       </c>
       <c r="F70" t="n">
-        <v>13.8533</v>
+        <v>14.5099</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>28.9428</v>
       </c>
     </row>
     <row r="71">
@@ -2470,17 +2470,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.9562</v>
+        <v>0.9321</v>
       </c>
       <c r="F71" t="n">
-        <v>12.6086</v>
+        <v>15.0314</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>28.5239</v>
       </c>
     </row>
     <row r="72">
@@ -2499,17 +2499,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.9638</v>
+        <v>0.9635</v>
       </c>
       <c r="F72" t="n">
-        <v>11.607</v>
+        <v>11.6482</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>28.103</v>
       </c>
     </row>
     <row r="73">
@@ -2528,17 +2528,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.9108000000000001</v>
+        <v>0.9102</v>
       </c>
       <c r="F73" t="n">
-        <v>16.6185</v>
+        <v>16.648</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>28.3211</v>
       </c>
     </row>
     <row r="74">
@@ -2557,17 +2557,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.9757</v>
+        <v>0.9759</v>
       </c>
       <c r="F74" t="n">
-        <v>10.0046</v>
+        <v>10.0006</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>27.9697</v>
       </c>
     </row>
     <row r="75">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.9678</v>
+        <v>0.9668</v>
       </c>
       <c r="F75" t="n">
-        <v>10.9406</v>
+        <v>11.2016</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>29.5253</v>
       </c>
     </row>
     <row r="76">
@@ -2615,17 +2615,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.9678</v>
+        <v>0.9668</v>
       </c>
       <c r="F76" t="n">
-        <v>10.9406</v>
+        <v>11.2016</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>29.5253</v>
       </c>
     </row>
     <row r="77">
@@ -2644,17 +2644,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.8802</v>
+        <v>0.8809</v>
       </c>
       <c r="F77" t="n">
-        <v>19.8177</v>
+        <v>19.7791</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>33.8084</v>
       </c>
     </row>
     <row r="78">
@@ -2673,17 +2673,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.8803</v>
+        <v>0.8809</v>
       </c>
       <c r="F78" t="n">
-        <v>19.7906</v>
+        <v>19.7544</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>33.7927</v>
       </c>
     </row>
     <row r="79">
@@ -2702,17 +2702,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.8796</v>
+        <v>0.8798</v>
       </c>
       <c r="F79" t="n">
-        <v>19.8591</v>
+        <v>19.8349</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>33.9858</v>
       </c>
     </row>
     <row r="80">
@@ -2731,17 +2731,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.8801</v>
+        <v>0.8807</v>
       </c>
       <c r="F80" t="n">
-        <v>19.794</v>
+        <v>19.7573</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>33.7878</v>
       </c>
     </row>
     <row r="81">
@@ -2760,17 +2760,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.8192</v>
+        <v>0.8194</v>
       </c>
       <c r="F81" t="n">
-        <v>23.7318</v>
+        <v>23.7247</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>35.3262</v>
       </c>
     </row>
     <row r="82">
@@ -2789,17 +2789,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.8401</v>
+        <v>0.8403</v>
       </c>
       <c r="F82" t="n">
-        <v>22.7701</v>
+        <v>22.7663</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>35.3547</v>
       </c>
     </row>
     <row r="83">
@@ -2818,17 +2818,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.9683</v>
+        <v>0.9689</v>
       </c>
       <c r="F83" t="n">
-        <v>10.9186</v>
+        <v>10.9605</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>29.5564</v>
       </c>
     </row>
     <row r="84">
@@ -2847,17 +2847,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.9673</v>
+        <v>0.9484</v>
       </c>
       <c r="F84" t="n">
-        <v>11.0425</v>
+        <v>13.2014</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>29.4423</v>
       </c>
     </row>
     <row r="85">
@@ -2876,17 +2876,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.9687</v>
+        <v>0.9695</v>
       </c>
       <c r="F85" t="n">
-        <v>10.8582</v>
+        <v>10.8963</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>29.3642</v>
       </c>
     </row>
     <row r="86">
@@ -2905,17 +2905,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E86" t="n">
         <v>0.9109</v>
       </c>
       <c r="F86" t="n">
-        <v>16.51</v>
+        <v>16.5022</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>28.2736</v>
       </c>
     </row>
     <row r="87">
@@ -2934,17 +2934,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.9689</v>
+        <v>0.9594</v>
       </c>
       <c r="F87" t="n">
-        <v>10.817</v>
+        <v>11.9686</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>28.3667</v>
       </c>
     </row>
     <row r="88">
@@ -2963,17 +2963,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.9633</v>
+        <v>0.9624</v>
       </c>
       <c r="F88" t="n">
-        <v>11.7068</v>
+        <v>11.774</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>28.6853</v>
       </c>
     </row>
     <row r="89">
@@ -2992,17 +2992,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.9755</v>
+        <v>0.9417</v>
       </c>
       <c r="F89" t="n">
-        <v>9.965400000000001</v>
+        <v>14.0662</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>28.317</v>
       </c>
     </row>
     <row r="90">
@@ -3021,17 +3021,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.9155</v>
+        <v>0.9249000000000001</v>
       </c>
       <c r="F90" t="n">
-        <v>17.0202</v>
+        <v>15.4552</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>27.2859</v>
       </c>
     </row>
     <row r="91">
@@ -3050,17 +3050,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E91" t="n">
         <v>0.9135</v>
       </c>
       <c r="F91" t="n">
-        <v>17</v>
+        <v>16.9973</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>27.1726</v>
       </c>
     </row>
     <row r="92">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.9633</v>
+        <v>0.9624</v>
       </c>
       <c r="F92" t="n">
-        <v>11.7068</v>
+        <v>11.774</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>28.6853</v>
       </c>
     </row>
     <row r="93">
@@ -3108,17 +3108,17 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E93" t="n">
         <v>0.9135</v>
       </c>
       <c r="F93" t="n">
-        <v>17</v>
+        <v>16.9973</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>27.1726</v>
       </c>
     </row>
     <row r="94">
@@ -3137,17 +3137,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.9381</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="F94" t="n">
-        <v>14.3493</v>
+        <v>14.3543</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>27.5826</v>
       </c>
     </row>
     <row r="95">
@@ -3166,17 +3166,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.7383999999999999</v>
+        <v>0.7389</v>
       </c>
       <c r="F95" t="n">
-        <v>28.1928</v>
+        <v>28.178</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>40.4234</v>
       </c>
     </row>
     <row r="96">
@@ -3195,17 +3195,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.9394</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="F96" t="n">
-        <v>14.2041</v>
+        <v>14.2318</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>27.8863</v>
       </c>
     </row>
     <row r="97">
@@ -3224,17 +3224,17 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.9387</v>
       </c>
       <c r="F97" t="n">
-        <v>14.2504</v>
+        <v>14.2626</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>27.9092</v>
       </c>
     </row>
     <row r="98">
@@ -3253,17 +3253,17 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.8988</v>
+        <v>0.8999</v>
       </c>
       <c r="F98" t="n">
-        <v>17.5489</v>
+        <v>17.4904</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>28.1908</v>
       </c>
     </row>
     <row r="99">
@@ -3282,17 +3282,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.8665</v>
+        <v>0.8667</v>
       </c>
       <c r="F99" t="n">
-        <v>19.8313</v>
+        <v>19.8238</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>28.7123</v>
       </c>
     </row>
     <row r="100">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.8776</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="F100" t="n">
-        <v>19.1378</v>
+        <v>19.1434</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>28.5269</v>
       </c>
     </row>
     <row r="101">
@@ -3340,17 +3340,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.8771</v>
+        <v>0.877</v>
       </c>
       <c r="F101" t="n">
-        <v>19.1705</v>
+        <v>19.1741</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>28.6031</v>
       </c>
     </row>
     <row r="102">
@@ -3369,17 +3369,17 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.8879</v>
+        <v>0.888</v>
       </c>
       <c r="F102" t="n">
-        <v>18.0139</v>
+        <v>18.0151</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>28.4604</v>
       </c>
     </row>
     <row r="103">
@@ -3398,17 +3398,17 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.9051</v>
+        <v>0.9046999999999999</v>
       </c>
       <c r="F103" t="n">
-        <v>16.9794</v>
+        <v>17.0032</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>28.6124</v>
       </c>
     </row>
     <row r="104">
@@ -3427,17 +3427,17 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.9016999999999999</v>
+        <v>0.9021</v>
       </c>
       <c r="F104" t="n">
-        <v>17.4141</v>
+        <v>17.3864</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>28.7256</v>
       </c>
     </row>
     <row r="105">
@@ -3456,17 +3456,17 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.9011</v>
+        <v>0.8991</v>
       </c>
       <c r="F105" t="n">
-        <v>17.6992</v>
+        <v>17.8042</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>28.7676</v>
       </c>
     </row>
     <row r="106">
@@ -3485,17 +3485,17 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.899</v>
+        <v>0.8992</v>
       </c>
       <c r="F106" t="n">
-        <v>17.7971</v>
+        <v>17.7693</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>28.4683</v>
       </c>
     </row>
     <row r="107">
@@ -3514,17 +3514,17 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E107" t="n">
         <v>0.8659</v>
       </c>
       <c r="F107" t="n">
-        <v>19.828</v>
+        <v>19.8296</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>28.6347</v>
       </c>
     </row>
     <row r="108">
@@ -3543,17 +3543,17 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.9678</v>
+        <v>0.968</v>
       </c>
       <c r="F108" t="n">
-        <v>11.1947</v>
+        <v>11.1535</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>27.4825</v>
       </c>
     </row>
     <row r="109">
@@ -3572,17 +3572,17 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.9512</v>
+        <v>0.9363</v>
       </c>
       <c r="F109" t="n">
-        <v>12.9477</v>
+        <v>14.2119</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>27.7995</v>
       </c>
     </row>
     <row r="110">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E110" t="n">
         <v>0.9096</v>
       </c>
       <c r="F110" t="n">
-        <v>16.785</v>
+        <v>16.7902</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>28.9028</v>
       </c>
     </row>
     <row r="111">
@@ -3630,17 +3630,17 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.9111</v>
+        <v>0.95</v>
       </c>
       <c r="F111" t="n">
-        <v>17.1164</v>
+        <v>13.6294</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>29.2827</v>
       </c>
     </row>
     <row r="112">
@@ -3659,17 +3659,17 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.9593</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="F112" t="n">
-        <v>12.1663</v>
+        <v>11.3432</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>27.5929</v>
       </c>
     </row>
     <row r="113">
@@ -3688,17 +3688,17 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.9518</v>
+        <v>0.9362</v>
       </c>
       <c r="F113" t="n">
-        <v>12.8587</v>
+        <v>14.2186</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>27.7953</v>
       </c>
     </row>
     <row r="114">
@@ -3717,17 +3717,17 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E114" t="n">
         <v>0.9106</v>
       </c>
       <c r="F114" t="n">
-        <v>16.6929</v>
+        <v>16.6984</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>28.9398</v>
       </c>
     </row>
     <row r="115">
@@ -3746,17 +3746,17 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.9499</v>
+        <v>0.9492</v>
       </c>
       <c r="F115" t="n">
-        <v>13.6365</v>
+        <v>13.7047</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>29.3299</v>
       </c>
     </row>
     <row r="116">
@@ -3775,17 +3775,17 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E116" t="n">
         <v>0.8047</v>
       </c>
       <c r="F116" t="n">
-        <v>24.3028</v>
+        <v>24.3067</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>35.5565</v>
       </c>
     </row>
     <row r="117">
@@ -3804,17 +3804,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.7994</v>
+        <v>0.7993</v>
       </c>
       <c r="F117" t="n">
-        <v>24.4258</v>
+        <v>24.4299</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>35.3984</v>
       </c>
     </row>
     <row r="118">
@@ -3833,17 +3833,17 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.9011</v>
+        <v>0.8991</v>
       </c>
       <c r="F118" t="n">
-        <v>17.6992</v>
+        <v>17.8042</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>28.7676</v>
       </c>
     </row>
     <row r="119">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.9518</v>
+        <v>0.9362</v>
       </c>
       <c r="F119" t="n">
-        <v>12.8587</v>
+        <v>14.2186</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>27.7953</v>
       </c>
     </row>
     <row r="120">
@@ -3891,17 +3891,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.8762</v>
+        <v>0.8763</v>
       </c>
       <c r="F120" t="n">
-        <v>18.9428</v>
+        <v>18.935</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>29.8948</v>
       </c>
     </row>
     <row r="121">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.8762</v>
+        <v>0.8763</v>
       </c>
       <c r="F121" t="n">
-        <v>18.9428</v>
+        <v>18.935</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>29.8948</v>
       </c>
     </row>
     <row r="122">
@@ -3949,17 +3949,17 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E122" t="n">
         <v>0.8799</v>
       </c>
       <c r="F122" t="n">
-        <v>18.6006</v>
+        <v>18.5949</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>29.5168</v>
       </c>
     </row>
     <row r="123">
@@ -3978,17 +3978,17 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.9518</v>
+        <v>0.9362</v>
       </c>
       <c r="F123" t="n">
-        <v>12.8589</v>
+        <v>14.2189</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>27.7886</v>
       </c>
     </row>
     <row r="124">
@@ -4007,17 +4007,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.9505</v>
+        <v>0.9509</v>
       </c>
       <c r="F124" t="n">
-        <v>12.953</v>
+        <v>12.9682</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>28.2467</v>
       </c>
     </row>
     <row r="125">
@@ -4036,17 +4036,17 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.9424</v>
+        <v>0.9426</v>
       </c>
       <c r="F125" t="n">
-        <v>14.0078</v>
+        <v>13.9818</v>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>27.811</v>
       </c>
     </row>
     <row r="126">
@@ -4065,17 +4065,17 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.8945</v>
+        <v>0.8944</v>
       </c>
       <c r="F126" t="n">
-        <v>17.6751</v>
+        <v>17.6916</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>29.2445</v>
       </c>
     </row>
     <row r="127">
@@ -4094,17 +4094,17 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E127" t="n">
         <v>0.7743</v>
       </c>
       <c r="F127" t="n">
-        <v>25.2553</v>
+        <v>25.2565</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>36.4627</v>
       </c>
     </row>
     <row r="128">
@@ -4123,17 +4123,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.8962</v>
+        <v>0.8963</v>
       </c>
       <c r="F128" t="n">
-        <v>17.5736</v>
+        <v>17.5701</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>29.0767</v>
       </c>
     </row>
     <row r="129">
@@ -4152,17 +4152,17 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.8986</v>
+        <v>0.8988</v>
       </c>
       <c r="F129" t="n">
-        <v>17.3671</v>
+        <v>17.3501</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>29.1456</v>
       </c>
     </row>
     <row r="130">
@@ -4181,17 +4181,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.8972</v>
+        <v>0.8975</v>
       </c>
       <c r="F130" t="n">
-        <v>17.4301</v>
+        <v>17.4129</v>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
+        <v>29.2118</v>
       </c>
     </row>
     <row r="131">
@@ -4210,17 +4210,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.8975</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="F131" t="n">
-        <v>17.4654</v>
+        <v>17.4673</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>29.1929</v>
       </c>
     </row>
     <row r="132">
@@ -4239,17 +4239,17 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.8976</v>
+        <v>0.8978</v>
       </c>
       <c r="F132" t="n">
-        <v>17.5574</v>
+        <v>17.5596</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>29.0798</v>
       </c>
     </row>
     <row r="133">
@@ -4268,17 +4268,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.8934</v>
+        <v>0.8938</v>
       </c>
       <c r="F133" t="n">
-        <v>17.8305</v>
+        <v>17.8195</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>29.0544</v>
       </c>
     </row>
     <row r="134">
@@ -4297,17 +4297,17 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.8964</v>
+        <v>0.8967000000000001</v>
       </c>
       <c r="F134" t="n">
-        <v>17.6472</v>
+        <v>17.635</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>29.0754</v>
       </c>
     </row>
     <row r="135">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0.8965</v>
+        <v>0.8966</v>
       </c>
       <c r="F135" t="n">
-        <v>17.6029</v>
+        <v>17.6013</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>29.0892</v>
       </c>
     </row>
     <row r="136">
@@ -4355,17 +4355,17 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.8971</v>
+        <v>0.8974</v>
       </c>
       <c r="F136" t="n">
-        <v>17.5168</v>
+        <v>17.51</v>
       </c>
       <c r="G136" t="n">
-        <v>0</v>
+        <v>29.1405</v>
       </c>
     </row>
     <row r="137">
@@ -4384,17 +4384,17 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.976</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="F137" t="n">
-        <v>9.9072</v>
+        <v>9.8649</v>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>27.8003</v>
       </c>
     </row>
     <row r="138">
@@ -4413,17 +4413,17 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.9738</v>
+        <v>0.9741</v>
       </c>
       <c r="F138" t="n">
-        <v>10.3517</v>
+        <v>10.3361</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>28.026</v>
       </c>
     </row>
     <row r="139">
@@ -4442,17 +4442,17 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.9769</v>
+        <v>0.9768</v>
       </c>
       <c r="F139" t="n">
-        <v>9.9176</v>
+        <v>9.9085</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>28.0653</v>
       </c>
     </row>
     <row r="140">
@@ -4471,17 +4471,17 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.9701</v>
+        <v>0.9705</v>
       </c>
       <c r="F140" t="n">
-        <v>10.6016</v>
+        <v>10.5632</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>27.2274</v>
       </c>
     </row>
     <row r="141">
@@ -4500,17 +4500,17 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.946</v>
+        <v>0.9464</v>
       </c>
       <c r="F141" t="n">
-        <v>13.2642</v>
+        <v>13.2282</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>26.6563</v>
       </c>
     </row>
     <row r="142">
@@ -4529,17 +4529,17 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.9738</v>
+        <v>0.9741</v>
       </c>
       <c r="F142" t="n">
-        <v>10.3517</v>
+        <v>10.3361</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>28.026</v>
       </c>
     </row>
     <row r="143">
@@ -4558,17 +4558,17 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.949</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="F143" t="n">
-        <v>13.1442</v>
+        <v>13.1549</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>28.0755</v>
       </c>
     </row>
     <row r="144">
@@ -4587,17 +4587,17 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.9516</v>
+        <v>0.9512</v>
       </c>
       <c r="F144" t="n">
-        <v>12.9483</v>
+        <v>12.9847</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>27.8628</v>
       </c>
     </row>
     <row r="145">
@@ -4616,17 +4616,17 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0.946</v>
+        <v>0.9464</v>
       </c>
       <c r="F145" t="n">
-        <v>13.2642</v>
+        <v>13.2282</v>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>26.6563</v>
       </c>
     </row>
     <row r="146">
@@ -4645,17 +4645,17 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.7721</v>
+        <v>0.7722</v>
       </c>
       <c r="F146" t="n">
-        <v>25.3198</v>
+        <v>25.3268</v>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>36.5276</v>
       </c>
     </row>
     <row r="147">
@@ -4674,17 +4674,17 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.7742</v>
+        <v>0.7745</v>
       </c>
       <c r="F147" t="n">
-        <v>25.2426</v>
+        <v>25.2433</v>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>36.441</v>
       </c>
     </row>
     <row r="148">
@@ -4703,17 +4703,17 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.7749</v>
+        <v>0.775</v>
       </c>
       <c r="F148" t="n">
-        <v>25.2302</v>
+        <v>25.2343</v>
       </c>
       <c r="G148" t="n">
-        <v>0</v>
+        <v>36.413</v>
       </c>
     </row>
     <row r="149">
@@ -4732,17 +4732,17 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.7719</v>
+        <v>0.7721</v>
       </c>
       <c r="F149" t="n">
         <v>25.2989</v>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>36.3784</v>
       </c>
     </row>
     <row r="150">
@@ -4761,17 +4761,17 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.7733</v>
+        <v>0.7735</v>
       </c>
       <c r="F150" t="n">
-        <v>25.2954</v>
+        <v>25.2923</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>36.5112</v>
       </c>
     </row>
     <row r="151">
@@ -4790,17 +4790,17 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.773</v>
       </c>
       <c r="F151" t="n">
-        <v>25.3023</v>
+        <v>25.2993</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>36.4953</v>
       </c>
     </row>
     <row r="152">
@@ -4819,17 +4819,17 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0.7731</v>
+        <v>0.7733</v>
       </c>
       <c r="F152" t="n">
-        <v>25.2822</v>
+        <v>25.2813</v>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>36.5065</v>
       </c>
     </row>
     <row r="153">
@@ -4848,17 +4848,17 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>0.7722</v>
+        <v>0.7724</v>
       </c>
       <c r="F153" t="n">
-        <v>25.316</v>
+        <v>25.3141</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>36.549</v>
       </c>
     </row>
     <row r="154">
@@ -4877,17 +4877,17 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.7738</v>
+        <v>0.7741</v>
       </c>
       <c r="F154" t="n">
-        <v>25.2464</v>
+        <v>25.2409</v>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
+        <v>36.4824</v>
       </c>
     </row>
     <row r="155">
@@ -4906,17 +4906,17 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.8135</v>
+        <v>0.8138</v>
       </c>
       <c r="F155" t="n">
-        <v>23.8266</v>
+        <v>23.8183</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>36.0436</v>
       </c>
     </row>
     <row r="156">
@@ -4935,17 +4935,17 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E156" t="n">
         <v>0.8103</v>
       </c>
       <c r="F156" t="n">
-        <v>23.9383</v>
+        <v>23.9384</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>35.9535</v>
       </c>
     </row>
     <row r="157">
@@ -4964,17 +4964,17 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E157" t="n">
         <v>0.8121</v>
       </c>
       <c r="F157" t="n">
-        <v>23.8812</v>
+        <v>23.8847</v>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>35.8143</v>
       </c>
     </row>
     <row r="158">
@@ -4993,17 +4993,17 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.824</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="F158" t="n">
-        <v>23.9158</v>
+        <v>23.9114</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>35.3704</v>
       </c>
     </row>
     <row r="159">
@@ -5022,17 +5022,17 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.8875999999999999</v>
+        <v>0.8939</v>
       </c>
       <c r="F159" t="n">
-        <v>18.125</v>
+        <v>17.4346</v>
       </c>
       <c r="G159" t="n">
-        <v>0</v>
+        <v>28.626</v>
       </c>
     </row>
     <row r="160">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.7877</v>
+        <v>0.7875</v>
       </c>
       <c r="F160" t="n">
-        <v>24.6975</v>
+        <v>24.7046</v>
       </c>
       <c r="G160" t="n">
-        <v>0</v>
+        <v>35.6036</v>
       </c>
     </row>
     <row r="161">
@@ -5080,17 +5080,17 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>0.7886</v>
+        <v>0.7885</v>
       </c>
       <c r="F161" t="n">
-        <v>24.6707</v>
+        <v>24.6798</v>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
+        <v>35.6305</v>
       </c>
     </row>
     <row r="162">
@@ -5109,17 +5109,17 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>0.8915999999999999</v>
+        <v>0.892</v>
       </c>
       <c r="F162" t="n">
-        <v>17.8202</v>
+        <v>17.8023</v>
       </c>
       <c r="G162" t="n">
-        <v>0</v>
+        <v>28.7434</v>
       </c>
     </row>
     <row r="163">
@@ -5138,17 +5138,17 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.954</v>
+        <v>0.9545</v>
       </c>
       <c r="F163" t="n">
-        <v>12.4912</v>
+        <v>12.4195</v>
       </c>
       <c r="G163" t="n">
-        <v>0</v>
+        <v>28.9869</v>
       </c>
     </row>
     <row r="164">
@@ -5167,17 +5167,17 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>0.9701</v>
+        <v>0.9706</v>
       </c>
       <c r="F164" t="n">
-        <v>10.6017</v>
+        <v>10.5569</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>27.2124</v>
       </c>
     </row>
     <row r="165">
@@ -5196,17 +5196,17 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.9424</v>
+        <v>0.9426</v>
       </c>
       <c r="F165" t="n">
-        <v>14.0078</v>
+        <v>13.9818</v>
       </c>
       <c r="G165" t="n">
-        <v>0</v>
+        <v>27.811</v>
       </c>
     </row>
     <row r="166">
@@ -5225,17 +5225,17 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.7504</v>
+        <v>0.7506</v>
       </c>
       <c r="F166" t="n">
-        <v>27.6886</v>
+        <v>27.6902</v>
       </c>
       <c r="G166" t="n">
-        <v>0</v>
+        <v>40.4488</v>
       </c>
     </row>
     <row r="167">
@@ -5254,17 +5254,17 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0.8823</v>
+        <v>0.882</v>
       </c>
       <c r="F167" t="n">
-        <v>18.505</v>
+        <v>18.5199</v>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>27.5427</v>
       </c>
     </row>
     <row r="168">
@@ -5283,17 +5283,17 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0.9217</v>
+        <v>0.9225</v>
       </c>
       <c r="F168" t="n">
-        <v>15.8371</v>
+        <v>15.7474</v>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>27.5304</v>
       </c>
     </row>
     <row r="169">
@@ -5312,17 +5312,17 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.9357</v>
+        <v>0.9479</v>
       </c>
       <c r="F169" t="n">
-        <v>14.7399</v>
+        <v>13.8074</v>
       </c>
       <c r="G169" t="n">
-        <v>0</v>
+        <v>27.6769</v>
       </c>
     </row>
     <row r="170">
@@ -5341,17 +5341,17 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>0.9727</v>
+        <v>0.9204</v>
       </c>
       <c r="F170" t="n">
-        <v>10.0548</v>
+        <v>16.2539</v>
       </c>
       <c r="G170" t="n">
-        <v>0</v>
+        <v>28.9269</v>
       </c>
     </row>
     <row r="171">
@@ -5370,17 +5370,17 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>0.9695</v>
+        <v>0.9704</v>
       </c>
       <c r="F171" t="n">
-        <v>10.5492</v>
+        <v>10.494</v>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>26.8505</v>
       </c>
     </row>
     <row r="172">
@@ -5399,17 +5399,17 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>0.9708</v>
+        <v>0.9215</v>
       </c>
       <c r="F172" t="n">
-        <v>10.2393</v>
+        <v>15.3925</v>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>28.5216</v>
       </c>
     </row>
   </sheetData>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/X13.cis.beta.carotene/RANDOMSEARCH_DETAILS_X13.cis.beta.carotene.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/X13.cis.beta.carotene/RANDOMSEARCH_DETAILS_X13.cis.beta.carotene.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G172"/>
+  <dimension ref="A1:H172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,10 +444,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>R2cv</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>RMSEC</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>RMSECV</t>
         </is>
@@ -476,9 +481,12 @@
         <v>0.9308</v>
       </c>
       <c r="F2" t="n">
+        <v>1.5394</v>
+      </c>
+      <c r="G2" t="n">
         <v>15.331</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>27.4919</v>
       </c>
     </row>
@@ -505,9 +513,12 @@
         <v>0.9676</v>
       </c>
       <c r="F3" t="n">
+        <v>1.5067</v>
+      </c>
+      <c r="G3" t="n">
         <v>11.2858</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>26.6443</v>
       </c>
     </row>
@@ -534,9 +545,12 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="F4" t="n">
+        <v>1.543</v>
+      </c>
+      <c r="G4" t="n">
         <v>14.3543</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>27.5826</v>
       </c>
     </row>
@@ -563,9 +577,12 @@
         <v>0.7895</v>
       </c>
       <c r="F5" t="n">
+        <v>1.8914</v>
+      </c>
+      <c r="G5" t="n">
         <v>24.8281</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>35.3411</v>
       </c>
     </row>
@@ -592,9 +609,12 @@
         <v>0.7756999999999999</v>
       </c>
       <c r="F6" t="n">
+        <v>1.9072</v>
+      </c>
+      <c r="G6" t="n">
         <v>25.2078</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>35.6516</v>
       </c>
     </row>
@@ -621,9 +641,12 @@
         <v>0.8905</v>
       </c>
       <c r="F7" t="n">
+        <v>1.5802</v>
+      </c>
+      <c r="G7" t="n">
         <v>18.17</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>28.5111</v>
       </c>
     </row>
@@ -650,9 +673,12 @@
         <v>0.8551</v>
       </c>
       <c r="F8" t="n">
+        <v>1.6228</v>
+      </c>
+      <c r="G8" t="n">
         <v>20.1</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>29.54</v>
       </c>
     </row>
@@ -679,9 +705,12 @@
         <v>0.9645</v>
       </c>
       <c r="F9" t="n">
+        <v>1.5176</v>
+      </c>
+      <c r="G9" t="n">
         <v>11.6891</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>26.929</v>
       </c>
     </row>
@@ -708,9 +737,12 @@
         <v>0.8574000000000001</v>
       </c>
       <c r="F10" t="n">
+        <v>1.6215</v>
+      </c>
+      <c r="G10" t="n">
         <v>19.9878</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>29.5095</v>
       </c>
     </row>
@@ -737,9 +769,12 @@
         <v>0.8571</v>
       </c>
       <c r="F11" t="n">
+        <v>1.6199</v>
+      </c>
+      <c r="G11" t="n">
         <v>19.9889</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>29.4708</v>
       </c>
     </row>
@@ -766,9 +801,12 @@
         <v>0.8569</v>
       </c>
       <c r="F12" t="n">
+        <v>1.6218</v>
+      </c>
+      <c r="G12" t="n">
         <v>19.9988</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>29.5153</v>
       </c>
     </row>
@@ -795,9 +833,12 @@
         <v>0.8568</v>
       </c>
       <c r="F13" t="n">
+        <v>1.621</v>
+      </c>
+      <c r="G13" t="n">
         <v>20.0011</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>29.498</v>
       </c>
     </row>
@@ -824,9 +865,12 @@
         <v>0.8572</v>
       </c>
       <c r="F14" t="n">
+        <v>1.6198</v>
+      </c>
+      <c r="G14" t="n">
         <v>19.9931</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>29.4698</v>
       </c>
     </row>
@@ -853,9 +897,12 @@
         <v>0.8572</v>
       </c>
       <c r="F15" t="n">
+        <v>1.6206</v>
+      </c>
+      <c r="G15" t="n">
         <v>19.9851</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>29.4889</v>
       </c>
     </row>
@@ -882,9 +929,12 @@
         <v>0.8577</v>
       </c>
       <c r="F16" t="n">
+        <v>1.6194</v>
+      </c>
+      <c r="G16" t="n">
         <v>19.9568</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>29.4599</v>
       </c>
     </row>
@@ -911,9 +961,12 @@
         <v>0.8569</v>
       </c>
       <c r="F17" t="n">
+        <v>1.6202</v>
+      </c>
+      <c r="G17" t="n">
         <v>20.005</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>29.4787</v>
       </c>
     </row>
@@ -940,9 +993,12 @@
         <v>0.894</v>
       </c>
       <c r="F18" t="n">
+        <v>1.5648</v>
+      </c>
+      <c r="G18" t="n">
         <v>17.9892</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>28.1301</v>
       </c>
     </row>
@@ -969,9 +1025,12 @@
         <v>0.8925999999999999</v>
       </c>
       <c r="F19" t="n">
+        <v>1.576</v>
+      </c>
+      <c r="G19" t="n">
         <v>18.0138</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>28.4087</v>
       </c>
     </row>
@@ -998,9 +1057,12 @@
         <v>0.8877</v>
       </c>
       <c r="F20" t="n">
+        <v>1.5716</v>
+      </c>
+      <c r="G20" t="n">
         <v>18.2639</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>28.3009</v>
       </c>
     </row>
@@ -1027,9 +1089,12 @@
         <v>0.8865</v>
       </c>
       <c r="F21" t="n">
+        <v>1.5858</v>
+      </c>
+      <c r="G21" t="n">
         <v>18.3379</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>28.6499</v>
       </c>
     </row>
@@ -1056,9 +1121,12 @@
         <v>0.8837</v>
       </c>
       <c r="F22" t="n">
+        <v>1.5871</v>
+      </c>
+      <c r="G22" t="n">
         <v>18.4765</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>28.6816</v>
       </c>
     </row>
@@ -1085,9 +1153,12 @@
         <v>0.885</v>
       </c>
       <c r="F23" t="n">
+        <v>1.5955</v>
+      </c>
+      <c r="G23" t="n">
         <v>18.4164</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>28.8859</v>
       </c>
     </row>
@@ -1114,9 +1185,12 @@
         <v>0.9458</v>
       </c>
       <c r="F24" t="n">
+        <v>1.5925</v>
+      </c>
+      <c r="G24" t="n">
         <v>13.4048</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>28.8134</v>
       </c>
     </row>
@@ -1143,9 +1217,12 @@
         <v>0.8663999999999999</v>
       </c>
       <c r="F25" t="n">
+        <v>1.5953</v>
+      </c>
+      <c r="G25" t="n">
         <v>19.4528</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>28.8812</v>
       </c>
     </row>
@@ -1172,9 +1249,12 @@
         <v>0.944</v>
       </c>
       <c r="F26" t="n">
+        <v>1.5684</v>
+      </c>
+      <c r="G26" t="n">
         <v>13.7728</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>28.2209</v>
       </c>
     </row>
@@ -1201,9 +1281,12 @@
         <v>0.9772999999999999</v>
       </c>
       <c r="F27" t="n">
+        <v>1.5661</v>
+      </c>
+      <c r="G27" t="n">
         <v>10</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>28.1644</v>
       </c>
     </row>
@@ -1230,9 +1313,12 @@
         <v>0.8945</v>
       </c>
       <c r="F28" t="n">
+        <v>1.5678</v>
+      </c>
+      <c r="G28" t="n">
         <v>17.9028</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>28.2046</v>
       </c>
     </row>
@@ -1259,9 +1345,12 @@
         <v>0.9761</v>
       </c>
       <c r="F29" t="n">
+        <v>1.5584</v>
+      </c>
+      <c r="G29" t="n">
         <v>10.0244</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>27.9714</v>
       </c>
     </row>
@@ -1288,9 +1377,12 @@
         <v>0.8753</v>
       </c>
       <c r="F30" t="n">
+        <v>1.5735</v>
+      </c>
+      <c r="G30" t="n">
         <v>19.0231</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>28.3479</v>
       </c>
     </row>
@@ -1317,9 +1409,12 @@
         <v>0.8833</v>
       </c>
       <c r="F31" t="n">
+        <v>1.5854</v>
+      </c>
+      <c r="G31" t="n">
         <v>18.5399</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>28.6398</v>
       </c>
     </row>
@@ -1346,9 +1441,12 @@
         <v>0.8878</v>
       </c>
       <c r="F32" t="n">
+        <v>1.5873</v>
+      </c>
+      <c r="G32" t="n">
         <v>18.2471</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>28.6868</v>
       </c>
     </row>
@@ -1375,9 +1473,12 @@
         <v>0.9732</v>
       </c>
       <c r="F33" t="n">
+        <v>1.5859</v>
+      </c>
+      <c r="G33" t="n">
         <v>10.6212</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>28.6509</v>
       </c>
     </row>
@@ -1404,9 +1505,12 @@
         <v>0.9398</v>
       </c>
       <c r="F34" t="n">
+        <v>1.5249</v>
+      </c>
+      <c r="G34" t="n">
         <v>13.8267</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>27.1181</v>
       </c>
     </row>
@@ -1433,9 +1537,12 @@
         <v>0.9389999999999999</v>
       </c>
       <c r="F35" t="n">
+        <v>1.5275</v>
+      </c>
+      <c r="G35" t="n">
         <v>13.8858</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>27.1855</v>
       </c>
     </row>
@@ -1462,9 +1569,12 @@
         <v>0.915</v>
       </c>
       <c r="F36" t="n">
+        <v>1.5328</v>
+      </c>
+      <c r="G36" t="n">
         <v>17.0506</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>27.3222</v>
       </c>
     </row>
@@ -1491,9 +1601,12 @@
         <v>0.9133</v>
       </c>
       <c r="F37" t="n">
+        <v>1.5299</v>
+      </c>
+      <c r="G37" t="n">
         <v>17</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>27.2485</v>
       </c>
     </row>
@@ -1520,9 +1633,12 @@
         <v>0.9069</v>
       </c>
       <c r="F38" t="n">
+        <v>1.5376</v>
+      </c>
+      <c r="G38" t="n">
         <v>17.3628</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>27.4442</v>
       </c>
     </row>
@@ -1549,9 +1665,12 @@
         <v>0.89</v>
       </c>
       <c r="F39" t="n">
+        <v>1.555</v>
+      </c>
+      <c r="G39" t="n">
         <v>18.4554</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>27.8853</v>
       </c>
     </row>
@@ -1578,9 +1697,12 @@
         <v>0.9055</v>
       </c>
       <c r="F40" t="n">
+        <v>1.5442</v>
+      </c>
+      <c r="G40" t="n">
         <v>17.2383</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>27.6123</v>
       </c>
     </row>
@@ -1607,9 +1729,12 @@
         <v>0.9403</v>
       </c>
       <c r="F41" t="n">
+        <v>1.523</v>
+      </c>
+      <c r="G41" t="n">
         <v>13.811</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>27.0709</v>
       </c>
     </row>
@@ -1636,9 +1761,12 @@
         <v>0.9389</v>
       </c>
       <c r="F42" t="n">
+        <v>1.5252</v>
+      </c>
+      <c r="G42" t="n">
         <v>13.8869</v>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>27.1259</v>
       </c>
     </row>
@@ -1665,9 +1793,12 @@
         <v>0.9249000000000001</v>
       </c>
       <c r="F43" t="n">
+        <v>1.5318</v>
+      </c>
+      <c r="G43" t="n">
         <v>15.4552</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>27.2956</v>
       </c>
     </row>
@@ -1694,9 +1825,12 @@
         <v>0.9135</v>
       </c>
       <c r="F44" t="n">
+        <v>1.5269</v>
+      </c>
+      <c r="G44" t="n">
         <v>16.9971</v>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>27.1713</v>
       </c>
     </row>
@@ -1723,9 +1857,12 @@
         <v>0.9078000000000001</v>
       </c>
       <c r="F45" t="n">
+        <v>1.5352</v>
+      </c>
+      <c r="G45" t="n">
         <v>17.3075</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>27.3845</v>
       </c>
     </row>
@@ -1752,9 +1889,12 @@
         <v>0.9157</v>
       </c>
       <c r="F46" t="n">
+        <v>1.5491</v>
+      </c>
+      <c r="G46" t="n">
         <v>16.5345</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>27.7367</v>
       </c>
     </row>
@@ -1781,9 +1921,12 @@
         <v>0.8887</v>
       </c>
       <c r="F47" t="n">
+        <v>1.5445</v>
+      </c>
+      <c r="G47" t="n">
         <v>18.4461</v>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>27.6215</v>
       </c>
     </row>
@@ -1810,9 +1953,12 @@
         <v>0.9159</v>
       </c>
       <c r="F48" t="n">
+        <v>1.5235</v>
+      </c>
+      <c r="G48" t="n">
         <v>16.8735</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>27.0833</v>
       </c>
     </row>
@@ -1839,9 +1985,12 @@
         <v>0.9305</v>
       </c>
       <c r="F49" t="n">
+        <v>1.5184</v>
+      </c>
+      <c r="G49" t="n">
         <v>14.9283</v>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>26.9496</v>
       </c>
     </row>
@@ -1868,9 +2017,12 @@
         <v>0.9028</v>
       </c>
       <c r="F50" t="n">
+        <v>1.8172</v>
+      </c>
+      <c r="G50" t="n">
         <v>19.7618</v>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>33.8379</v>
       </c>
     </row>
@@ -1897,9 +2049,12 @@
         <v>0.8331</v>
       </c>
       <c r="F51" t="n">
+        <v>1.8561</v>
+      </c>
+      <c r="G51" t="n">
         <v>23.4596</v>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
         <v>34.634</v>
       </c>
     </row>
@@ -1926,9 +2081,12 @@
         <v>0.8336</v>
       </c>
       <c r="F52" t="n">
+        <v>1.8501</v>
+      </c>
+      <c r="G52" t="n">
         <v>23.4385</v>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>34.5121</v>
       </c>
     </row>
@@ -1955,9 +2113,12 @@
         <v>0.8502999999999999</v>
       </c>
       <c r="F53" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="G53" t="n">
         <v>22.7599</v>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
         <v>33.8948</v>
       </c>
     </row>
@@ -1984,9 +2145,12 @@
         <v>0.8739</v>
       </c>
       <c r="F54" t="n">
+        <v>1.8029</v>
+      </c>
+      <c r="G54" t="n">
         <v>20.7312</v>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
         <v>33.5407</v>
       </c>
     </row>
@@ -2013,9 +2177,12 @@
         <v>0.8587</v>
       </c>
       <c r="F55" t="n">
+        <v>1.8448</v>
+      </c>
+      <c r="G55" t="n">
         <v>21.848</v>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>34.4035</v>
       </c>
     </row>
@@ -2042,9 +2209,12 @@
         <v>0.9011</v>
       </c>
       <c r="F56" t="n">
+        <v>1.8064</v>
+      </c>
+      <c r="G56" t="n">
         <v>19.2681</v>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>33.6129</v>
       </c>
     </row>
@@ -2071,9 +2241,12 @@
         <v>0.8488</v>
       </c>
       <c r="F57" t="n">
+        <v>1.8284</v>
+      </c>
+      <c r="G57" t="n">
         <v>22.6746</v>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>34.0693</v>
       </c>
     </row>
@@ -2100,9 +2273,12 @@
         <v>0.7772</v>
       </c>
       <c r="F58" t="n">
+        <v>1.9077</v>
+      </c>
+      <c r="G58" t="n">
         <v>25.173</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>35.6617</v>
       </c>
     </row>
@@ -2129,9 +2305,12 @@
         <v>0.7774</v>
       </c>
       <c r="F59" t="n">
+        <v>1.9065</v>
+      </c>
+      <c r="G59" t="n">
         <v>25.1655</v>
       </c>
-      <c r="G59" t="n">
+      <c r="H59" t="n">
         <v>35.6385</v>
       </c>
     </row>
@@ -2158,9 +2337,12 @@
         <v>0.7776</v>
       </c>
       <c r="F60" t="n">
+        <v>1.9058</v>
+      </c>
+      <c r="G60" t="n">
         <v>25.1502</v>
       </c>
-      <c r="G60" t="n">
+      <c r="H60" t="n">
         <v>35.6239</v>
       </c>
     </row>
@@ -2187,9 +2369,12 @@
         <v>0.7786999999999999</v>
       </c>
       <c r="F61" t="n">
+        <v>1.9069</v>
+      </c>
+      <c r="G61" t="n">
         <v>25.1075</v>
       </c>
-      <c r="G61" t="n">
+      <c r="H61" t="n">
         <v>35.6471</v>
       </c>
     </row>
@@ -2216,9 +2401,12 @@
         <v>0.8122</v>
       </c>
       <c r="F62" t="n">
+        <v>1.9147</v>
+      </c>
+      <c r="G62" t="n">
         <v>23.9425</v>
       </c>
-      <c r="G62" t="n">
+      <c r="H62" t="n">
         <v>35.7992</v>
       </c>
     </row>
@@ -2245,9 +2433,12 @@
         <v>0.8168</v>
       </c>
       <c r="F63" t="n">
+        <v>1.9135</v>
+      </c>
+      <c r="G63" t="n">
         <v>23.7081</v>
       </c>
-      <c r="G63" t="n">
+      <c r="H63" t="n">
         <v>35.7762</v>
       </c>
     </row>
@@ -2274,9 +2465,12 @@
         <v>0.8649</v>
       </c>
       <c r="F64" t="n">
+        <v>1.915</v>
+      </c>
+      <c r="G64" t="n">
         <v>21.5597</v>
       </c>
-      <c r="G64" t="n">
+      <c r="H64" t="n">
         <v>35.8058</v>
       </c>
     </row>
@@ -2303,9 +2497,12 @@
         <v>0.8635</v>
       </c>
       <c r="F65" t="n">
+        <v>1.9143</v>
+      </c>
+      <c r="G65" t="n">
         <v>21.5804</v>
       </c>
-      <c r="G65" t="n">
+      <c r="H65" t="n">
         <v>35.7921</v>
       </c>
     </row>
@@ -2332,9 +2529,12 @@
         <v>0.9583</v>
       </c>
       <c r="F66" t="n">
+        <v>1.8213</v>
+      </c>
+      <c r="G66" t="n">
         <v>14.4913</v>
       </c>
-      <c r="G66" t="n">
+      <c r="H66" t="n">
         <v>33.9232</v>
       </c>
     </row>
@@ -2361,9 +2561,12 @@
         <v>0.8854</v>
       </c>
       <c r="F67" t="n">
+        <v>1.8217</v>
+      </c>
+      <c r="G67" t="n">
         <v>20.3074</v>
       </c>
-      <c r="G67" t="n">
+      <c r="H67" t="n">
         <v>33.9311</v>
       </c>
     </row>
@@ -2390,9 +2593,12 @@
         <v>0.8645</v>
       </c>
       <c r="F68" t="n">
+        <v>1.8241</v>
+      </c>
+      <c r="G68" t="n">
         <v>21.7712</v>
       </c>
-      <c r="G68" t="n">
+      <c r="H68" t="n">
         <v>33.9799</v>
       </c>
     </row>
@@ -2419,9 +2625,12 @@
         <v>0.9429</v>
       </c>
       <c r="F69" t="n">
+        <v>1.5817</v>
+      </c>
+      <c r="G69" t="n">
         <v>13.8199</v>
       </c>
-      <c r="G69" t="n">
+      <c r="H69" t="n">
         <v>28.5488</v>
       </c>
     </row>
@@ -2448,9 +2657,12 @@
         <v>0.9358</v>
       </c>
       <c r="F70" t="n">
+        <v>1.5979</v>
+      </c>
+      <c r="G70" t="n">
         <v>14.5099</v>
       </c>
-      <c r="G70" t="n">
+      <c r="H70" t="n">
         <v>28.9428</v>
       </c>
     </row>
@@ -2477,9 +2689,12 @@
         <v>0.9321</v>
       </c>
       <c r="F71" t="n">
+        <v>1.5807</v>
+      </c>
+      <c r="G71" t="n">
         <v>15.0314</v>
       </c>
-      <c r="G71" t="n">
+      <c r="H71" t="n">
         <v>28.5239</v>
       </c>
     </row>
@@ -2506,9 +2721,12 @@
         <v>0.9635</v>
       </c>
       <c r="F72" t="n">
+        <v>1.5637</v>
+      </c>
+      <c r="G72" t="n">
         <v>11.6482</v>
       </c>
-      <c r="G72" t="n">
+      <c r="H72" t="n">
         <v>28.103</v>
       </c>
     </row>
@@ -2535,9 +2753,12 @@
         <v>0.9102</v>
       </c>
       <c r="F73" t="n">
+        <v>1.5725</v>
+      </c>
+      <c r="G73" t="n">
         <v>16.648</v>
       </c>
-      <c r="G73" t="n">
+      <c r="H73" t="n">
         <v>28.3211</v>
       </c>
     </row>
@@ -2564,9 +2785,12 @@
         <v>0.9759</v>
       </c>
       <c r="F74" t="n">
+        <v>1.5583</v>
+      </c>
+      <c r="G74" t="n">
         <v>10.0006</v>
       </c>
-      <c r="G74" t="n">
+      <c r="H74" t="n">
         <v>27.9697</v>
       </c>
     </row>
@@ -2593,9 +2817,12 @@
         <v>0.9668</v>
       </c>
       <c r="F75" t="n">
+        <v>1.6222</v>
+      </c>
+      <c r="G75" t="n">
         <v>11.2016</v>
       </c>
-      <c r="G75" t="n">
+      <c r="H75" t="n">
         <v>29.5253</v>
       </c>
     </row>
@@ -2622,9 +2849,12 @@
         <v>0.9668</v>
       </c>
       <c r="F76" t="n">
+        <v>1.6222</v>
+      </c>
+      <c r="G76" t="n">
         <v>11.2016</v>
       </c>
-      <c r="G76" t="n">
+      <c r="H76" t="n">
         <v>29.5253</v>
       </c>
     </row>
@@ -2644,16 +2874,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E77" t="n">
         <v>0.8809</v>
       </c>
       <c r="F77" t="n">
+        <v>1.8158</v>
+      </c>
+      <c r="G77" t="n">
         <v>19.7791</v>
       </c>
-      <c r="G77" t="n">
+      <c r="H77" t="n">
         <v>33.8084</v>
       </c>
     </row>
@@ -2680,9 +2913,12 @@
         <v>0.8809</v>
       </c>
       <c r="F78" t="n">
+        <v>1.815</v>
+      </c>
+      <c r="G78" t="n">
         <v>19.7544</v>
       </c>
-      <c r="G78" t="n">
+      <c r="H78" t="n">
         <v>33.7927</v>
       </c>
     </row>
@@ -2709,9 +2945,12 @@
         <v>0.8798</v>
       </c>
       <c r="F79" t="n">
+        <v>1.8244</v>
+      </c>
+      <c r="G79" t="n">
         <v>19.8349</v>
       </c>
-      <c r="G79" t="n">
+      <c r="H79" t="n">
         <v>33.9858</v>
       </c>
     </row>
@@ -2738,9 +2977,12 @@
         <v>0.8807</v>
       </c>
       <c r="F80" t="n">
+        <v>1.8148</v>
+      </c>
+      <c r="G80" t="n">
         <v>19.7573</v>
       </c>
-      <c r="G80" t="n">
+      <c r="H80" t="n">
         <v>33.7878</v>
       </c>
     </row>
@@ -2767,9 +3009,12 @@
         <v>0.8194</v>
       </c>
       <c r="F81" t="n">
+        <v>1.8907</v>
+      </c>
+      <c r="G81" t="n">
         <v>23.7247</v>
       </c>
-      <c r="G81" t="n">
+      <c r="H81" t="n">
         <v>35.3262</v>
       </c>
     </row>
@@ -2796,9 +3041,12 @@
         <v>0.8403</v>
       </c>
       <c r="F82" t="n">
+        <v>1.8921</v>
+      </c>
+      <c r="G82" t="n">
         <v>22.7663</v>
       </c>
-      <c r="G82" t="n">
+      <c r="H82" t="n">
         <v>35.3547</v>
       </c>
     </row>
@@ -2825,9 +3073,12 @@
         <v>0.9689</v>
       </c>
       <c r="F83" t="n">
+        <v>1.6235</v>
+      </c>
+      <c r="G83" t="n">
         <v>10.9605</v>
       </c>
-      <c r="G83" t="n">
+      <c r="H83" t="n">
         <v>29.5564</v>
       </c>
     </row>
@@ -2854,9 +3105,12 @@
         <v>0.9484</v>
       </c>
       <c r="F84" t="n">
+        <v>1.6187</v>
+      </c>
+      <c r="G84" t="n">
         <v>13.2014</v>
       </c>
-      <c r="G84" t="n">
+      <c r="H84" t="n">
         <v>29.4423</v>
       </c>
     </row>
@@ -2883,9 +3137,12 @@
         <v>0.9695</v>
       </c>
       <c r="F85" t="n">
+        <v>1.6154</v>
+      </c>
+      <c r="G85" t="n">
         <v>10.8963</v>
       </c>
-      <c r="G85" t="n">
+      <c r="H85" t="n">
         <v>29.3642</v>
       </c>
     </row>
@@ -2912,9 +3169,12 @@
         <v>0.9109</v>
       </c>
       <c r="F86" t="n">
+        <v>1.5705</v>
+      </c>
+      <c r="G86" t="n">
         <v>16.5022</v>
       </c>
-      <c r="G86" t="n">
+      <c r="H86" t="n">
         <v>28.2736</v>
       </c>
     </row>
@@ -2941,9 +3201,12 @@
         <v>0.9594</v>
       </c>
       <c r="F87" t="n">
+        <v>1.5743</v>
+      </c>
+      <c r="G87" t="n">
         <v>11.9686</v>
       </c>
-      <c r="G87" t="n">
+      <c r="H87" t="n">
         <v>28.3667</v>
       </c>
     </row>
@@ -2970,9 +3233,12 @@
         <v>0.9624</v>
       </c>
       <c r="F88" t="n">
+        <v>1.5873</v>
+      </c>
+      <c r="G88" t="n">
         <v>11.774</v>
       </c>
-      <c r="G88" t="n">
+      <c r="H88" t="n">
         <v>28.6853</v>
       </c>
     </row>
@@ -2999,9 +3265,12 @@
         <v>0.9417</v>
       </c>
       <c r="F89" t="n">
+        <v>1.5723</v>
+      </c>
+      <c r="G89" t="n">
         <v>14.0662</v>
       </c>
-      <c r="G89" t="n">
+      <c r="H89" t="n">
         <v>28.317</v>
       </c>
     </row>
@@ -3028,9 +3297,12 @@
         <v>0.9249000000000001</v>
       </c>
       <c r="F90" t="n">
+        <v>1.5314</v>
+      </c>
+      <c r="G90" t="n">
         <v>15.4552</v>
       </c>
-      <c r="G90" t="n">
+      <c r="H90" t="n">
         <v>27.2859</v>
       </c>
     </row>
@@ -3057,9 +3329,12 @@
         <v>0.9135</v>
       </c>
       <c r="F91" t="n">
+        <v>1.527</v>
+      </c>
+      <c r="G91" t="n">
         <v>16.9973</v>
       </c>
-      <c r="G91" t="n">
+      <c r="H91" t="n">
         <v>27.1726</v>
       </c>
     </row>
@@ -3086,9 +3361,12 @@
         <v>0.9624</v>
       </c>
       <c r="F92" t="n">
+        <v>1.5873</v>
+      </c>
+      <c r="G92" t="n">
         <v>11.774</v>
       </c>
-      <c r="G92" t="n">
+      <c r="H92" t="n">
         <v>28.6853</v>
       </c>
     </row>
@@ -3115,9 +3393,12 @@
         <v>0.9135</v>
       </c>
       <c r="F93" t="n">
+        <v>1.527</v>
+      </c>
+      <c r="G93" t="n">
         <v>16.9973</v>
       </c>
-      <c r="G93" t="n">
+      <c r="H93" t="n">
         <v>27.1726</v>
       </c>
     </row>
@@ -3144,9 +3425,12 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="F94" t="n">
+        <v>1.543</v>
+      </c>
+      <c r="G94" t="n">
         <v>14.3543</v>
       </c>
-      <c r="G94" t="n">
+      <c r="H94" t="n">
         <v>27.5826</v>
       </c>
     </row>
@@ -3173,9 +3457,12 @@
         <v>0.7389</v>
       </c>
       <c r="F95" t="n">
+        <v>2.1663</v>
+      </c>
+      <c r="G95" t="n">
         <v>28.178</v>
       </c>
-      <c r="G95" t="n">
+      <c r="H95" t="n">
         <v>40.4234</v>
       </c>
     </row>
@@ -3202,9 +3489,12 @@
         <v>0.9389999999999999</v>
       </c>
       <c r="F96" t="n">
+        <v>1.555</v>
+      </c>
+      <c r="G96" t="n">
         <v>14.2318</v>
       </c>
-      <c r="G96" t="n">
+      <c r="H96" t="n">
         <v>27.8863</v>
       </c>
     </row>
@@ -3231,9 +3521,12 @@
         <v>0.9387</v>
       </c>
       <c r="F97" t="n">
+        <v>1.5559</v>
+      </c>
+      <c r="G97" t="n">
         <v>14.2626</v>
       </c>
-      <c r="G97" t="n">
+      <c r="H97" t="n">
         <v>27.9092</v>
       </c>
     </row>
@@ -3260,9 +3553,12 @@
         <v>0.8999</v>
       </c>
       <c r="F98" t="n">
+        <v>1.5672</v>
+      </c>
+      <c r="G98" t="n">
         <v>17.4904</v>
       </c>
-      <c r="G98" t="n">
+      <c r="H98" t="n">
         <v>28.1908</v>
       </c>
     </row>
@@ -3289,9 +3585,12 @@
         <v>0.8667</v>
       </c>
       <c r="F99" t="n">
+        <v>1.5884</v>
+      </c>
+      <c r="G99" t="n">
         <v>19.8238</v>
       </c>
-      <c r="G99" t="n">
+      <c r="H99" t="n">
         <v>28.7123</v>
       </c>
     </row>
@@ -3318,9 +3617,12 @@
         <v>0.8774999999999999</v>
       </c>
       <c r="F100" t="n">
+        <v>1.5808</v>
+      </c>
+      <c r="G100" t="n">
         <v>19.1434</v>
       </c>
-      <c r="G100" t="n">
+      <c r="H100" t="n">
         <v>28.5269</v>
       </c>
     </row>
@@ -3347,9 +3649,12 @@
         <v>0.877</v>
       </c>
       <c r="F101" t="n">
+        <v>1.5839</v>
+      </c>
+      <c r="G101" t="n">
         <v>19.1741</v>
       </c>
-      <c r="G101" t="n">
+      <c r="H101" t="n">
         <v>28.6031</v>
       </c>
     </row>
@@ -3369,16 +3674,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E102" t="n">
         <v>0.888</v>
       </c>
       <c r="F102" t="n">
-        <v>18.0151</v>
+        <v>1.5781</v>
       </c>
       <c r="G102" t="n">
+        <v>18.0147</v>
+      </c>
+      <c r="H102" t="n">
         <v>28.4604</v>
       </c>
     </row>
@@ -3405,9 +3713,12 @@
         <v>0.9046999999999999</v>
       </c>
       <c r="F103" t="n">
+        <v>1.5843</v>
+      </c>
+      <c r="G103" t="n">
         <v>17.0032</v>
       </c>
-      <c r="G103" t="n">
+      <c r="H103" t="n">
         <v>28.6124</v>
       </c>
     </row>
@@ -3434,9 +3745,12 @@
         <v>0.9021</v>
       </c>
       <c r="F104" t="n">
+        <v>1.5889</v>
+      </c>
+      <c r="G104" t="n">
         <v>17.3864</v>
       </c>
-      <c r="G104" t="n">
+      <c r="H104" t="n">
         <v>28.7256</v>
       </c>
     </row>
@@ -3463,9 +3777,12 @@
         <v>0.8991</v>
       </c>
       <c r="F105" t="n">
+        <v>1.5907</v>
+      </c>
+      <c r="G105" t="n">
         <v>17.8042</v>
       </c>
-      <c r="G105" t="n">
+      <c r="H105" t="n">
         <v>28.7676</v>
       </c>
     </row>
@@ -3492,9 +3809,12 @@
         <v>0.8992</v>
       </c>
       <c r="F106" t="n">
+        <v>1.5784</v>
+      </c>
+      <c r="G106" t="n">
         <v>17.7693</v>
       </c>
-      <c r="G106" t="n">
+      <c r="H106" t="n">
         <v>28.4683</v>
       </c>
     </row>
@@ -3521,9 +3841,12 @@
         <v>0.8659</v>
       </c>
       <c r="F107" t="n">
+        <v>1.5852</v>
+      </c>
+      <c r="G107" t="n">
         <v>19.8296</v>
       </c>
-      <c r="G107" t="n">
+      <c r="H107" t="n">
         <v>28.6347</v>
       </c>
     </row>
@@ -3550,9 +3873,12 @@
         <v>0.968</v>
       </c>
       <c r="F108" t="n">
+        <v>1.5391</v>
+      </c>
+      <c r="G108" t="n">
         <v>11.1535</v>
       </c>
-      <c r="G108" t="n">
+      <c r="H108" t="n">
         <v>27.4825</v>
       </c>
     </row>
@@ -3579,9 +3905,12 @@
         <v>0.9363</v>
       </c>
       <c r="F109" t="n">
+        <v>1.5516</v>
+      </c>
+      <c r="G109" t="n">
         <v>14.2119</v>
       </c>
-      <c r="G109" t="n">
+      <c r="H109" t="n">
         <v>27.7995</v>
       </c>
     </row>
@@ -3608,9 +3937,12 @@
         <v>0.9096</v>
       </c>
       <c r="F110" t="n">
+        <v>1.5962</v>
+      </c>
+      <c r="G110" t="n">
         <v>16.7902</v>
       </c>
-      <c r="G110" t="n">
+      <c r="H110" t="n">
         <v>28.9028</v>
       </c>
     </row>
@@ -3637,9 +3969,12 @@
         <v>0.95</v>
       </c>
       <c r="F111" t="n">
+        <v>1.612</v>
+      </c>
+      <c r="G111" t="n">
         <v>13.6294</v>
       </c>
-      <c r="G111" t="n">
+      <c r="H111" t="n">
         <v>29.2827</v>
       </c>
     </row>
@@ -3666,9 +4001,12 @@
         <v>0.9661999999999999</v>
       </c>
       <c r="F112" t="n">
+        <v>1.5434</v>
+      </c>
+      <c r="G112" t="n">
         <v>11.3432</v>
       </c>
-      <c r="G112" t="n">
+      <c r="H112" t="n">
         <v>27.5929</v>
       </c>
     </row>
@@ -3695,9 +4033,12 @@
         <v>0.9362</v>
       </c>
       <c r="F113" t="n">
+        <v>1.5514</v>
+      </c>
+      <c r="G113" t="n">
         <v>14.2186</v>
       </c>
-      <c r="G113" t="n">
+      <c r="H113" t="n">
         <v>27.7953</v>
       </c>
     </row>
@@ -3724,9 +4065,12 @@
         <v>0.9106</v>
       </c>
       <c r="F114" t="n">
+        <v>1.5977</v>
+      </c>
+      <c r="G114" t="n">
         <v>16.6984</v>
       </c>
-      <c r="G114" t="n">
+      <c r="H114" t="n">
         <v>28.9398</v>
       </c>
     </row>
@@ -3753,9 +4097,12 @@
         <v>0.9492</v>
       </c>
       <c r="F115" t="n">
+        <v>1.614</v>
+      </c>
+      <c r="G115" t="n">
         <v>13.7047</v>
       </c>
-      <c r="G115" t="n">
+      <c r="H115" t="n">
         <v>29.3299</v>
       </c>
     </row>
@@ -3782,9 +4129,12 @@
         <v>0.8047</v>
       </c>
       <c r="F116" t="n">
+        <v>1.9023</v>
+      </c>
+      <c r="G116" t="n">
         <v>24.3067</v>
       </c>
-      <c r="G116" t="n">
+      <c r="H116" t="n">
         <v>35.5565</v>
       </c>
     </row>
@@ -3811,9 +4161,12 @@
         <v>0.7993</v>
       </c>
       <c r="F117" t="n">
+        <v>1.8943</v>
+      </c>
+      <c r="G117" t="n">
         <v>24.4299</v>
       </c>
-      <c r="G117" t="n">
+      <c r="H117" t="n">
         <v>35.3984</v>
       </c>
     </row>
@@ -3840,9 +4193,12 @@
         <v>0.8991</v>
       </c>
       <c r="F118" t="n">
+        <v>1.5907</v>
+      </c>
+      <c r="G118" t="n">
         <v>17.8042</v>
       </c>
-      <c r="G118" t="n">
+      <c r="H118" t="n">
         <v>28.7676</v>
       </c>
     </row>
@@ -3869,9 +4225,12 @@
         <v>0.9362</v>
       </c>
       <c r="F119" t="n">
+        <v>1.5514</v>
+      </c>
+      <c r="G119" t="n">
         <v>14.2186</v>
       </c>
-      <c r="G119" t="n">
+      <c r="H119" t="n">
         <v>27.7953</v>
       </c>
     </row>
@@ -3898,9 +4257,12 @@
         <v>0.8763</v>
       </c>
       <c r="F120" t="n">
+        <v>1.6378</v>
+      </c>
+      <c r="G120" t="n">
         <v>18.935</v>
       </c>
-      <c r="G120" t="n">
+      <c r="H120" t="n">
         <v>29.8948</v>
       </c>
     </row>
@@ -3927,9 +4289,12 @@
         <v>0.8763</v>
       </c>
       <c r="F121" t="n">
+        <v>1.6378</v>
+      </c>
+      <c r="G121" t="n">
         <v>18.935</v>
       </c>
-      <c r="G121" t="n">
+      <c r="H121" t="n">
         <v>29.8948</v>
       </c>
     </row>
@@ -3956,9 +4321,12 @@
         <v>0.8799</v>
       </c>
       <c r="F122" t="n">
+        <v>1.6218</v>
+      </c>
+      <c r="G122" t="n">
         <v>18.5949</v>
       </c>
-      <c r="G122" t="n">
+      <c r="H122" t="n">
         <v>29.5168</v>
       </c>
     </row>
@@ -3985,9 +4353,12 @@
         <v>0.9362</v>
       </c>
       <c r="F123" t="n">
+        <v>1.5511</v>
+      </c>
+      <c r="G123" t="n">
         <v>14.2189</v>
       </c>
-      <c r="G123" t="n">
+      <c r="H123" t="n">
         <v>27.7886</v>
       </c>
     </row>
@@ -4014,9 +4385,12 @@
         <v>0.9509</v>
       </c>
       <c r="F124" t="n">
+        <v>1.5695</v>
+      </c>
+      <c r="G124" t="n">
         <v>12.9682</v>
       </c>
-      <c r="G124" t="n">
+      <c r="H124" t="n">
         <v>28.2467</v>
       </c>
     </row>
@@ -4043,9 +4417,12 @@
         <v>0.9426</v>
       </c>
       <c r="F125" t="n">
+        <v>1.552</v>
+      </c>
+      <c r="G125" t="n">
         <v>13.9818</v>
       </c>
-      <c r="G125" t="n">
+      <c r="H125" t="n">
         <v>27.811</v>
       </c>
     </row>
@@ -4072,9 +4449,12 @@
         <v>0.8944</v>
       </c>
       <c r="F126" t="n">
+        <v>1.6104</v>
+      </c>
+      <c r="G126" t="n">
         <v>17.6916</v>
       </c>
-      <c r="G126" t="n">
+      <c r="H126" t="n">
         <v>29.2445</v>
       </c>
     </row>
@@ -4101,9 +4481,12 @@
         <v>0.7743</v>
       </c>
       <c r="F127" t="n">
+        <v>1.9489</v>
+      </c>
+      <c r="G127" t="n">
         <v>25.2565</v>
       </c>
-      <c r="G127" t="n">
+      <c r="H127" t="n">
         <v>36.4627</v>
       </c>
     </row>
@@ -4130,9 +4513,12 @@
         <v>0.8963</v>
       </c>
       <c r="F128" t="n">
+        <v>1.6034</v>
+      </c>
+      <c r="G128" t="n">
         <v>17.5701</v>
       </c>
-      <c r="G128" t="n">
+      <c r="H128" t="n">
         <v>29.0767</v>
       </c>
     </row>
@@ -4159,9 +4545,12 @@
         <v>0.8988</v>
       </c>
       <c r="F129" t="n">
+        <v>1.6063</v>
+      </c>
+      <c r="G129" t="n">
         <v>17.3501</v>
       </c>
-      <c r="G129" t="n">
+      <c r="H129" t="n">
         <v>29.1456</v>
       </c>
     </row>
@@ -4188,9 +4577,12 @@
         <v>0.8975</v>
       </c>
       <c r="F130" t="n">
+        <v>1.609</v>
+      </c>
+      <c r="G130" t="n">
         <v>17.4129</v>
       </c>
-      <c r="G130" t="n">
+      <c r="H130" t="n">
         <v>29.2118</v>
       </c>
     </row>
@@ -4217,9 +4609,12 @@
         <v>0.8977000000000001</v>
       </c>
       <c r="F131" t="n">
+        <v>1.6082</v>
+      </c>
+      <c r="G131" t="n">
         <v>17.4673</v>
       </c>
-      <c r="G131" t="n">
+      <c r="H131" t="n">
         <v>29.1929</v>
       </c>
     </row>
@@ -4246,9 +4641,12 @@
         <v>0.8978</v>
       </c>
       <c r="F132" t="n">
+        <v>1.6035</v>
+      </c>
+      <c r="G132" t="n">
         <v>17.5596</v>
       </c>
-      <c r="G132" t="n">
+      <c r="H132" t="n">
         <v>29.0798</v>
       </c>
     </row>
@@ -4275,9 +4673,12 @@
         <v>0.8938</v>
       </c>
       <c r="F133" t="n">
+        <v>1.6025</v>
+      </c>
+      <c r="G133" t="n">
         <v>17.8195</v>
       </c>
-      <c r="G133" t="n">
+      <c r="H133" t="n">
         <v>29.0544</v>
       </c>
     </row>
@@ -4304,9 +4705,12 @@
         <v>0.8967000000000001</v>
       </c>
       <c r="F134" t="n">
+        <v>1.6034</v>
+      </c>
+      <c r="G134" t="n">
         <v>17.635</v>
       </c>
-      <c r="G134" t="n">
+      <c r="H134" t="n">
         <v>29.0754</v>
       </c>
     </row>
@@ -4333,9 +4737,12 @@
         <v>0.8966</v>
       </c>
       <c r="F135" t="n">
+        <v>1.6039</v>
+      </c>
+      <c r="G135" t="n">
         <v>17.6013</v>
       </c>
-      <c r="G135" t="n">
+      <c r="H135" t="n">
         <v>29.0892</v>
       </c>
     </row>
@@ -4362,9 +4769,12 @@
         <v>0.8974</v>
       </c>
       <c r="F136" t="n">
+        <v>1.6061</v>
+      </c>
+      <c r="G136" t="n">
         <v>17.51</v>
       </c>
-      <c r="G136" t="n">
+      <c r="H136" t="n">
         <v>29.1405</v>
       </c>
     </row>
@@ -4391,9 +4801,12 @@
         <v>0.9762999999999999</v>
       </c>
       <c r="F137" t="n">
+        <v>1.5516</v>
+      </c>
+      <c r="G137" t="n">
         <v>9.8649</v>
       </c>
-      <c r="G137" t="n">
+      <c r="H137" t="n">
         <v>27.8003</v>
       </c>
     </row>
@@ -4420,9 +4833,12 @@
         <v>0.9741</v>
       </c>
       <c r="F138" t="n">
+        <v>1.5606</v>
+      </c>
+      <c r="G138" t="n">
         <v>10.3361</v>
       </c>
-      <c r="G138" t="n">
+      <c r="H138" t="n">
         <v>28.026</v>
       </c>
     </row>
@@ -4449,9 +4865,12 @@
         <v>0.9768</v>
       </c>
       <c r="F139" t="n">
+        <v>1.5622</v>
+      </c>
+      <c r="G139" t="n">
         <v>9.9085</v>
       </c>
-      <c r="G139" t="n">
+      <c r="H139" t="n">
         <v>28.0653</v>
       </c>
     </row>
@@ -4478,9 +4897,12 @@
         <v>0.9705</v>
       </c>
       <c r="F140" t="n">
+        <v>1.5291</v>
+      </c>
+      <c r="G140" t="n">
         <v>10.5632</v>
       </c>
-      <c r="G140" t="n">
+      <c r="H140" t="n">
         <v>27.2274</v>
       </c>
     </row>
@@ -4507,9 +4929,12 @@
         <v>0.9464</v>
       </c>
       <c r="F141" t="n">
+        <v>1.5071</v>
+      </c>
+      <c r="G141" t="n">
         <v>13.2282</v>
       </c>
-      <c r="G141" t="n">
+      <c r="H141" t="n">
         <v>26.6563</v>
       </c>
     </row>
@@ -4536,9 +4961,12 @@
         <v>0.9741</v>
       </c>
       <c r="F142" t="n">
+        <v>1.5606</v>
+      </c>
+      <c r="G142" t="n">
         <v>10.3361</v>
       </c>
-      <c r="G142" t="n">
+      <c r="H142" t="n">
         <v>28.026</v>
       </c>
     </row>
@@ -4565,9 +4993,12 @@
         <v>0.9491000000000001</v>
       </c>
       <c r="F143" t="n">
+        <v>1.5626</v>
+      </c>
+      <c r="G143" t="n">
         <v>13.1549</v>
       </c>
-      <c r="G143" t="n">
+      <c r="H143" t="n">
         <v>28.0755</v>
       </c>
     </row>
@@ -4594,9 +5025,12 @@
         <v>0.9512</v>
       </c>
       <c r="F144" t="n">
+        <v>1.5541</v>
+      </c>
+      <c r="G144" t="n">
         <v>12.9847</v>
       </c>
-      <c r="G144" t="n">
+      <c r="H144" t="n">
         <v>27.8628</v>
       </c>
     </row>
@@ -4623,9 +5057,12 @@
         <v>0.9464</v>
       </c>
       <c r="F145" t="n">
+        <v>1.5071</v>
+      </c>
+      <c r="G145" t="n">
         <v>13.2282</v>
       </c>
-      <c r="G145" t="n">
+      <c r="H145" t="n">
         <v>26.6563</v>
       </c>
     </row>
@@ -4652,9 +5089,12 @@
         <v>0.7722</v>
       </c>
       <c r="F146" t="n">
+        <v>1.9523</v>
+      </c>
+      <c r="G146" t="n">
         <v>25.3268</v>
       </c>
-      <c r="G146" t="n">
+      <c r="H146" t="n">
         <v>36.5276</v>
       </c>
     </row>
@@ -4681,9 +5121,12 @@
         <v>0.7745</v>
       </c>
       <c r="F147" t="n">
+        <v>1.9478</v>
+      </c>
+      <c r="G147" t="n">
         <v>25.2433</v>
       </c>
-      <c r="G147" t="n">
+      <c r="H147" t="n">
         <v>36.441</v>
       </c>
     </row>
@@ -4710,9 +5153,12 @@
         <v>0.775</v>
       </c>
       <c r="F148" t="n">
+        <v>1.9463</v>
+      </c>
+      <c r="G148" t="n">
         <v>25.2343</v>
       </c>
-      <c r="G148" t="n">
+      <c r="H148" t="n">
         <v>36.413</v>
       </c>
     </row>
@@ -4739,9 +5185,12 @@
         <v>0.7721</v>
       </c>
       <c r="F149" t="n">
+        <v>1.9445</v>
+      </c>
+      <c r="G149" t="n">
         <v>25.2989</v>
       </c>
-      <c r="G149" t="n">
+      <c r="H149" t="n">
         <v>36.3784</v>
       </c>
     </row>
@@ -4768,9 +5217,12 @@
         <v>0.7735</v>
       </c>
       <c r="F150" t="n">
+        <v>1.9514</v>
+      </c>
+      <c r="G150" t="n">
         <v>25.2923</v>
       </c>
-      <c r="G150" t="n">
+      <c r="H150" t="n">
         <v>36.5112</v>
       </c>
     </row>
@@ -4797,9 +5249,12 @@
         <v>0.773</v>
       </c>
       <c r="F151" t="n">
+        <v>1.9506</v>
+      </c>
+      <c r="G151" t="n">
         <v>25.2993</v>
       </c>
-      <c r="G151" t="n">
+      <c r="H151" t="n">
         <v>36.4953</v>
       </c>
     </row>
@@ -4826,9 +5281,12 @@
         <v>0.7733</v>
       </c>
       <c r="F152" t="n">
+        <v>1.9512</v>
+      </c>
+      <c r="G152" t="n">
         <v>25.2813</v>
       </c>
-      <c r="G152" t="n">
+      <c r="H152" t="n">
         <v>36.5065</v>
       </c>
     </row>
@@ -4855,9 +5313,12 @@
         <v>0.7724</v>
       </c>
       <c r="F153" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="G153" t="n">
         <v>25.3141</v>
       </c>
-      <c r="G153" t="n">
+      <c r="H153" t="n">
         <v>36.549</v>
       </c>
     </row>
@@ -4884,9 +5345,12 @@
         <v>0.7741</v>
       </c>
       <c r="F154" t="n">
+        <v>1.9499</v>
+      </c>
+      <c r="G154" t="n">
         <v>25.2409</v>
       </c>
-      <c r="G154" t="n">
+      <c r="H154" t="n">
         <v>36.4824</v>
       </c>
     </row>
@@ -4913,9 +5377,12 @@
         <v>0.8138</v>
       </c>
       <c r="F155" t="n">
+        <v>1.9272</v>
+      </c>
+      <c r="G155" t="n">
         <v>23.8183</v>
       </c>
-      <c r="G155" t="n">
+      <c r="H155" t="n">
         <v>36.0436</v>
       </c>
     </row>
@@ -4942,9 +5409,12 @@
         <v>0.8103</v>
       </c>
       <c r="F156" t="n">
+        <v>1.9226</v>
+      </c>
+      <c r="G156" t="n">
         <v>23.9384</v>
       </c>
-      <c r="G156" t="n">
+      <c r="H156" t="n">
         <v>35.9535</v>
       </c>
     </row>
@@ -4971,9 +5441,12 @@
         <v>0.8121</v>
       </c>
       <c r="F157" t="n">
+        <v>1.9155</v>
+      </c>
+      <c r="G157" t="n">
         <v>23.8847</v>
       </c>
-      <c r="G157" t="n">
+      <c r="H157" t="n">
         <v>35.8143</v>
       </c>
     </row>
@@ -5000,9 +5473,12 @@
         <v>0.8241000000000001</v>
       </c>
       <c r="F158" t="n">
+        <v>1.8929</v>
+      </c>
+      <c r="G158" t="n">
         <v>23.9114</v>
       </c>
-      <c r="G158" t="n">
+      <c r="H158" t="n">
         <v>35.3704</v>
       </c>
     </row>
@@ -5029,9 +5505,12 @@
         <v>0.8939</v>
       </c>
       <c r="F159" t="n">
+        <v>1.5849</v>
+      </c>
+      <c r="G159" t="n">
         <v>17.4346</v>
       </c>
-      <c r="G159" t="n">
+      <c r="H159" t="n">
         <v>28.626</v>
       </c>
     </row>
@@ -5058,9 +5537,12 @@
         <v>0.7875</v>
       </c>
       <c r="F160" t="n">
+        <v>1.9047</v>
+      </c>
+      <c r="G160" t="n">
         <v>24.7046</v>
       </c>
-      <c r="G160" t="n">
+      <c r="H160" t="n">
         <v>35.6036</v>
       </c>
     </row>
@@ -5087,9 +5569,12 @@
         <v>0.7885</v>
       </c>
       <c r="F161" t="n">
+        <v>1.9061</v>
+      </c>
+      <c r="G161" t="n">
         <v>24.6798</v>
       </c>
-      <c r="G161" t="n">
+      <c r="H161" t="n">
         <v>35.6305</v>
       </c>
     </row>
@@ -5116,9 +5601,12 @@
         <v>0.892</v>
       </c>
       <c r="F162" t="n">
+        <v>1.5897</v>
+      </c>
+      <c r="G162" t="n">
         <v>17.8023</v>
       </c>
-      <c r="G162" t="n">
+      <c r="H162" t="n">
         <v>28.7434</v>
       </c>
     </row>
@@ -5145,9 +5633,12 @@
         <v>0.9545</v>
       </c>
       <c r="F163" t="n">
+        <v>1.5997</v>
+      </c>
+      <c r="G163" t="n">
         <v>12.4195</v>
       </c>
-      <c r="G163" t="n">
+      <c r="H163" t="n">
         <v>28.9869</v>
       </c>
     </row>
@@ -5174,9 +5665,12 @@
         <v>0.9706</v>
       </c>
       <c r="F164" t="n">
+        <v>1.5285</v>
+      </c>
+      <c r="G164" t="n">
         <v>10.5569</v>
       </c>
-      <c r="G164" t="n">
+      <c r="H164" t="n">
         <v>27.2124</v>
       </c>
     </row>
@@ -5203,9 +5697,12 @@
         <v>0.9426</v>
       </c>
       <c r="F165" t="n">
+        <v>1.552</v>
+      </c>
+      <c r="G165" t="n">
         <v>13.9818</v>
       </c>
-      <c r="G165" t="n">
+      <c r="H165" t="n">
         <v>27.811</v>
       </c>
     </row>
@@ -5232,9 +5729,12 @@
         <v>0.7506</v>
       </c>
       <c r="F166" t="n">
+        <v>2.1677</v>
+      </c>
+      <c r="G166" t="n">
         <v>27.6902</v>
       </c>
-      <c r="G166" t="n">
+      <c r="H166" t="n">
         <v>40.4488</v>
       </c>
     </row>
@@ -5261,9 +5761,12 @@
         <v>0.882</v>
       </c>
       <c r="F167" t="n">
+        <v>1.5414</v>
+      </c>
+      <c r="G167" t="n">
         <v>18.5199</v>
       </c>
-      <c r="G167" t="n">
+      <c r="H167" t="n">
         <v>27.5427</v>
       </c>
     </row>
@@ -5290,9 +5793,12 @@
         <v>0.9225</v>
       </c>
       <c r="F168" t="n">
+        <v>1.5409</v>
+      </c>
+      <c r="G168" t="n">
         <v>15.7474</v>
       </c>
-      <c r="G168" t="n">
+      <c r="H168" t="n">
         <v>27.5304</v>
       </c>
     </row>
@@ -5319,9 +5825,12 @@
         <v>0.9479</v>
       </c>
       <c r="F169" t="n">
+        <v>1.5467</v>
+      </c>
+      <c r="G169" t="n">
         <v>13.8074</v>
       </c>
-      <c r="G169" t="n">
+      <c r="H169" t="n">
         <v>27.6769</v>
       </c>
     </row>
@@ -5348,9 +5857,12 @@
         <v>0.9204</v>
       </c>
       <c r="F170" t="n">
+        <v>1.5972</v>
+      </c>
+      <c r="G170" t="n">
         <v>16.2539</v>
       </c>
-      <c r="G170" t="n">
+      <c r="H170" t="n">
         <v>28.9269</v>
       </c>
     </row>
@@ -5377,9 +5889,12 @@
         <v>0.9704</v>
       </c>
       <c r="F171" t="n">
+        <v>1.5146</v>
+      </c>
+      <c r="G171" t="n">
         <v>10.494</v>
       </c>
-      <c r="G171" t="n">
+      <c r="H171" t="n">
         <v>26.8505</v>
       </c>
     </row>
@@ -5406,9 +5921,12 @@
         <v>0.9215</v>
       </c>
       <c r="F172" t="n">
+        <v>1.5806</v>
+      </c>
+      <c r="G172" t="n">
         <v>15.3925</v>
       </c>
-      <c r="G172" t="n">
+      <c r="H172" t="n">
         <v>28.5216</v>
       </c>
     </row>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/X13.cis.beta.carotene/RANDOMSEARCH_DETAILS_X13.cis.beta.carotene.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/X13.cis.beta.carotene/RANDOMSEARCH_DETAILS_X13.cis.beta.carotene.xlsx
@@ -474,20 +474,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9308</v>
+        <v>0.9323</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5394</v>
+        <v>0.3567</v>
       </c>
       <c r="G2" t="n">
-        <v>15.331</v>
+        <v>15.3555</v>
       </c>
       <c r="H2" t="n">
-        <v>27.4919</v>
+        <v>30.103</v>
       </c>
     </row>
     <row r="3">
@@ -506,20 +506,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9676</v>
+        <v>0.9776</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5067</v>
+        <v>0.3742</v>
       </c>
       <c r="G3" t="n">
-        <v>11.2858</v>
+        <v>10.5827</v>
       </c>
       <c r="H3" t="n">
-        <v>26.6443</v>
+        <v>29.6911</v>
       </c>
     </row>
     <row r="4">
@@ -538,20 +538,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9673</v>
       </c>
       <c r="F4" t="n">
-        <v>1.543</v>
+        <v>0.4454</v>
       </c>
       <c r="G4" t="n">
-        <v>14.3543</v>
+        <v>10.976</v>
       </c>
       <c r="H4" t="n">
-        <v>27.5826</v>
+        <v>27.9517</v>
       </c>
     </row>
     <row r="5">
@@ -574,16 +574,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.7895</v>
+        <v>0.7654</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8914</v>
+        <v>0.0239</v>
       </c>
       <c r="G5" t="n">
-        <v>24.8281</v>
+        <v>25.8412</v>
       </c>
       <c r="H5" t="n">
-        <v>35.3411</v>
+        <v>37.0825</v>
       </c>
     </row>
     <row r="6">
@@ -606,16 +606,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.7756999999999999</v>
+        <v>0.7604</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9072</v>
+        <v>0.0175</v>
       </c>
       <c r="G6" t="n">
-        <v>25.2078</v>
+        <v>26.0357</v>
       </c>
       <c r="H6" t="n">
-        <v>35.6516</v>
+        <v>37.203</v>
       </c>
     </row>
     <row r="7">
@@ -634,20 +634,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.8905</v>
+        <v>0.8768</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5802</v>
+        <v>0.3612</v>
       </c>
       <c r="G7" t="n">
-        <v>18.17</v>
+        <v>18.9888</v>
       </c>
       <c r="H7" t="n">
-        <v>28.5111</v>
+        <v>29.9972</v>
       </c>
     </row>
     <row r="8">
@@ -666,20 +666,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.8551</v>
+        <v>0.8662</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6228</v>
+        <v>0.2815</v>
       </c>
       <c r="G8" t="n">
-        <v>20.1</v>
+        <v>19.7474</v>
       </c>
       <c r="H8" t="n">
-        <v>29.54</v>
+        <v>31.8156</v>
       </c>
     </row>
     <row r="9">
@@ -698,20 +698,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.9645</v>
+        <v>0.9107</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5176</v>
+        <v>0.3986</v>
       </c>
       <c r="G9" t="n">
-        <v>11.6891</v>
+        <v>17.0466</v>
       </c>
       <c r="H9" t="n">
-        <v>26.929</v>
+        <v>29.1066</v>
       </c>
     </row>
     <row r="10">
@@ -730,20 +730,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.8574000000000001</v>
+        <v>0.9575</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6215</v>
+        <v>0.2965</v>
       </c>
       <c r="G10" t="n">
-        <v>19.9878</v>
+        <v>12.2183</v>
       </c>
       <c r="H10" t="n">
-        <v>29.5095</v>
+        <v>31.481</v>
       </c>
     </row>
     <row r="11">
@@ -766,16 +766,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.8571</v>
+        <v>0.8329</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6199</v>
+        <v>0.2819</v>
       </c>
       <c r="G11" t="n">
-        <v>19.9889</v>
+        <v>21.452</v>
       </c>
       <c r="H11" t="n">
-        <v>29.4708</v>
+        <v>31.8063</v>
       </c>
     </row>
     <row r="12">
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.8569</v>
+        <v>0.8329</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6218</v>
+        <v>0.2782</v>
       </c>
       <c r="G12" t="n">
-        <v>19.9988</v>
+        <v>21.455</v>
       </c>
       <c r="H12" t="n">
-        <v>29.5153</v>
+        <v>31.887</v>
       </c>
     </row>
     <row r="13">
@@ -830,16 +830,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.8568</v>
+        <v>0.831</v>
       </c>
       <c r="F13" t="n">
-        <v>1.621</v>
+        <v>0.2791</v>
       </c>
       <c r="G13" t="n">
-        <v>20.0011</v>
+        <v>21.5282</v>
       </c>
       <c r="H13" t="n">
-        <v>29.498</v>
+        <v>31.8666</v>
       </c>
     </row>
     <row r="14">
@@ -862,16 +862,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.8572</v>
+        <v>0.8328</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6198</v>
+        <v>0.2817</v>
       </c>
       <c r="G14" t="n">
-        <v>19.9931</v>
+        <v>21.4592</v>
       </c>
       <c r="H14" t="n">
-        <v>29.4698</v>
+        <v>31.8098</v>
       </c>
     </row>
     <row r="15">
@@ -894,16 +894,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.8572</v>
+        <v>0.8327</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6206</v>
+        <v>0.279</v>
       </c>
       <c r="G15" t="n">
-        <v>19.9851</v>
+        <v>21.4682</v>
       </c>
       <c r="H15" t="n">
-        <v>29.4889</v>
+        <v>31.8689</v>
       </c>
     </row>
     <row r="16">
@@ -926,16 +926,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.8577</v>
+        <v>0.8327</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6194</v>
+        <v>0.2765</v>
       </c>
       <c r="G16" t="n">
-        <v>19.9568</v>
+        <v>21.4691</v>
       </c>
       <c r="H16" t="n">
-        <v>29.4599</v>
+        <v>31.9247</v>
       </c>
     </row>
     <row r="17">
@@ -958,16 +958,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.8569</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6202</v>
+        <v>0.2781</v>
       </c>
       <c r="G17" t="n">
-        <v>20.005</v>
+        <v>21.5278</v>
       </c>
       <c r="H17" t="n">
-        <v>29.4787</v>
+        <v>31.8908</v>
       </c>
     </row>
     <row r="18">
@@ -990,16 +990,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.894</v>
+        <v>0.8739</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5648</v>
+        <v>0.3454</v>
       </c>
       <c r="G18" t="n">
-        <v>17.9892</v>
+        <v>19.5278</v>
       </c>
       <c r="H18" t="n">
-        <v>28.1301</v>
+        <v>30.3676</v>
       </c>
     </row>
     <row r="19">
@@ -1018,20 +1018,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.8925999999999999</v>
+        <v>0.8551</v>
       </c>
       <c r="F19" t="n">
-        <v>1.576</v>
+        <v>0.3424</v>
       </c>
       <c r="G19" t="n">
-        <v>18.0138</v>
+        <v>20.5728</v>
       </c>
       <c r="H19" t="n">
-        <v>28.4087</v>
+        <v>30.4374</v>
       </c>
     </row>
     <row r="20">
@@ -1050,20 +1050,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.8877</v>
+        <v>0.8924</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5716</v>
+        <v>0.3497</v>
       </c>
       <c r="G20" t="n">
-        <v>18.2639</v>
+        <v>18.3604</v>
       </c>
       <c r="H20" t="n">
-        <v>28.3009</v>
+        <v>30.2676</v>
       </c>
     </row>
     <row r="21">
@@ -1082,20 +1082,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.8865</v>
+        <v>0.8466</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5858</v>
+        <v>0.3493</v>
       </c>
       <c r="G21" t="n">
-        <v>18.3379</v>
+        <v>20.8851</v>
       </c>
       <c r="H21" t="n">
-        <v>28.6499</v>
+        <v>30.2753</v>
       </c>
     </row>
     <row r="22">
@@ -1114,20 +1114,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.8837</v>
+        <v>0.8798</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5871</v>
+        <v>0.3405</v>
       </c>
       <c r="G22" t="n">
-        <v>18.4765</v>
+        <v>19.1221</v>
       </c>
       <c r="H22" t="n">
-        <v>28.6816</v>
+        <v>30.4794</v>
       </c>
     </row>
     <row r="23">
@@ -1146,20 +1146,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.885</v>
+        <v>0.8475</v>
       </c>
       <c r="F23" t="n">
-        <v>1.5955</v>
+        <v>0.3367</v>
       </c>
       <c r="G23" t="n">
-        <v>18.4164</v>
+        <v>20.8582</v>
       </c>
       <c r="H23" t="n">
-        <v>28.8859</v>
+        <v>30.5672</v>
       </c>
     </row>
     <row r="24">
@@ -1178,20 +1178,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.9458</v>
+        <v>0.887</v>
       </c>
       <c r="F24" t="n">
-        <v>1.5925</v>
+        <v>0.3345</v>
       </c>
       <c r="G24" t="n">
-        <v>13.4048</v>
+        <v>18.7218</v>
       </c>
       <c r="H24" t="n">
-        <v>28.8134</v>
+        <v>30.6193</v>
       </c>
     </row>
     <row r="25">
@@ -1210,20 +1210,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.8834</v>
       </c>
       <c r="F25" t="n">
-        <v>1.5953</v>
+        <v>0.3297</v>
       </c>
       <c r="G25" t="n">
-        <v>19.4528</v>
+        <v>18.6924</v>
       </c>
       <c r="H25" t="n">
-        <v>28.8812</v>
+        <v>30.7298</v>
       </c>
     </row>
     <row r="26">
@@ -1242,20 +1242,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.944</v>
+        <v>0.8601</v>
       </c>
       <c r="F26" t="n">
-        <v>1.5684</v>
+        <v>0.3515</v>
       </c>
       <c r="G26" t="n">
-        <v>13.7728</v>
+        <v>20.4159</v>
       </c>
       <c r="H26" t="n">
-        <v>28.2209</v>
+        <v>30.2243</v>
       </c>
     </row>
     <row r="27">
@@ -1274,20 +1274,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.8892</v>
       </c>
       <c r="F27" t="n">
-        <v>1.5661</v>
+        <v>0.3566</v>
       </c>
       <c r="G27" t="n">
-        <v>10</v>
+        <v>18.7519</v>
       </c>
       <c r="H27" t="n">
-        <v>28.1644</v>
+        <v>30.1069</v>
       </c>
     </row>
     <row r="28">
@@ -1306,20 +1306,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.8945</v>
+        <v>0.8576</v>
       </c>
       <c r="F28" t="n">
-        <v>1.5678</v>
+        <v>0.3488</v>
       </c>
       <c r="G28" t="n">
-        <v>17.9028</v>
+        <v>20.5076</v>
       </c>
       <c r="H28" t="n">
-        <v>28.2046</v>
+        <v>30.2886</v>
       </c>
     </row>
     <row r="29">
@@ -1338,20 +1338,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.9761</v>
+        <v>0.8957000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>1.5584</v>
+        <v>0.3599</v>
       </c>
       <c r="G29" t="n">
-        <v>10.0244</v>
+        <v>18.221</v>
       </c>
       <c r="H29" t="n">
-        <v>27.9714</v>
+        <v>30.0296</v>
       </c>
     </row>
     <row r="30">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.8753</v>
+        <v>0.8541</v>
       </c>
       <c r="F30" t="n">
-        <v>1.5735</v>
+        <v>0.3544</v>
       </c>
       <c r="G30" t="n">
-        <v>19.0231</v>
+        <v>20.5562</v>
       </c>
       <c r="H30" t="n">
-        <v>28.3479</v>
+        <v>30.1577</v>
       </c>
     </row>
     <row r="31">
@@ -1402,20 +1402,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.8833</v>
+        <v>0.8475</v>
       </c>
       <c r="F31" t="n">
-        <v>1.5854</v>
+        <v>0.344</v>
       </c>
       <c r="G31" t="n">
-        <v>18.5399</v>
+        <v>20.8487</v>
       </c>
       <c r="H31" t="n">
-        <v>28.6398</v>
+        <v>30.3992</v>
       </c>
     </row>
     <row r="32">
@@ -1434,20 +1434,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.8878</v>
+        <v>0.8894</v>
       </c>
       <c r="F32" t="n">
-        <v>1.5873</v>
+        <v>0.3438</v>
       </c>
       <c r="G32" t="n">
-        <v>18.2471</v>
+        <v>18.6374</v>
       </c>
       <c r="H32" t="n">
-        <v>28.6868</v>
+        <v>30.4032</v>
       </c>
     </row>
     <row r="33">
@@ -1466,20 +1466,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.9732</v>
+        <v>0.9353</v>
       </c>
       <c r="F33" t="n">
-        <v>1.5859</v>
+        <v>0.3426</v>
       </c>
       <c r="G33" t="n">
-        <v>10.6212</v>
+        <v>14.9448</v>
       </c>
       <c r="H33" t="n">
-        <v>28.6509</v>
+        <v>30.4312</v>
       </c>
     </row>
     <row r="34">
@@ -1498,20 +1498,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9398</v>
+        <v>0.9308</v>
       </c>
       <c r="F34" t="n">
-        <v>1.5249</v>
+        <v>0.4165</v>
       </c>
       <c r="G34" t="n">
-        <v>13.8267</v>
+        <v>15.0294</v>
       </c>
       <c r="H34" t="n">
-        <v>27.1181</v>
+        <v>28.6691</v>
       </c>
     </row>
     <row r="35">
@@ -1530,20 +1530,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.9222</v>
       </c>
       <c r="F35" t="n">
-        <v>1.5275</v>
+        <v>0.3958</v>
       </c>
       <c r="G35" t="n">
-        <v>13.8858</v>
+        <v>17.2291</v>
       </c>
       <c r="H35" t="n">
-        <v>27.1855</v>
+        <v>29.1732</v>
       </c>
     </row>
     <row r="36">
@@ -1566,16 +1566,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.915</v>
+        <v>0.905</v>
       </c>
       <c r="F36" t="n">
-        <v>1.5328</v>
+        <v>0.3934</v>
       </c>
       <c r="G36" t="n">
-        <v>17.0506</v>
+        <v>18.2514</v>
       </c>
       <c r="H36" t="n">
-        <v>27.3222</v>
+        <v>29.2324</v>
       </c>
     </row>
     <row r="37">
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.9133</v>
+        <v>0.9044</v>
       </c>
       <c r="F37" t="n">
-        <v>1.5299</v>
+        <v>0.3905</v>
       </c>
       <c r="G37" t="n">
-        <v>17</v>
+        <v>18.1293</v>
       </c>
       <c r="H37" t="n">
-        <v>27.2485</v>
+        <v>29.3029</v>
       </c>
     </row>
     <row r="38">
@@ -1626,20 +1626,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.9069</v>
+        <v>0.9054</v>
       </c>
       <c r="F38" t="n">
-        <v>1.5376</v>
+        <v>0.3905</v>
       </c>
       <c r="G38" t="n">
-        <v>17.3628</v>
+        <v>17.3942</v>
       </c>
       <c r="H38" t="n">
-        <v>27.4442</v>
+        <v>29.3018</v>
       </c>
     </row>
     <row r="39">
@@ -1662,16 +1662,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.89</v>
+        <v>0.8739</v>
       </c>
       <c r="F39" t="n">
-        <v>1.555</v>
+        <v>0.3697</v>
       </c>
       <c r="G39" t="n">
-        <v>18.4554</v>
+        <v>19.7667</v>
       </c>
       <c r="H39" t="n">
-        <v>27.8853</v>
+        <v>29.7986</v>
       </c>
     </row>
     <row r="40">
@@ -1690,20 +1690,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.9055</v>
+        <v>0.8702</v>
       </c>
       <c r="F40" t="n">
-        <v>1.5442</v>
+        <v>0.3863</v>
       </c>
       <c r="G40" t="n">
-        <v>17.2383</v>
+        <v>19.9224</v>
       </c>
       <c r="H40" t="n">
-        <v>27.6123</v>
+        <v>29.4038</v>
       </c>
     </row>
     <row r="41">
@@ -1722,20 +1722,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.9403</v>
+        <v>0.93</v>
       </c>
       <c r="F41" t="n">
-        <v>1.523</v>
+        <v>0.4172</v>
       </c>
       <c r="G41" t="n">
-        <v>13.811</v>
+        <v>15.0975</v>
       </c>
       <c r="H41" t="n">
-        <v>27.0709</v>
+        <v>28.6534</v>
       </c>
     </row>
     <row r="42">
@@ -1754,20 +1754,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.9389</v>
+        <v>0.9307</v>
       </c>
       <c r="F42" t="n">
-        <v>1.5252</v>
+        <v>0.3972</v>
       </c>
       <c r="G42" t="n">
-        <v>13.8869</v>
+        <v>15.0635</v>
       </c>
       <c r="H42" t="n">
-        <v>27.1259</v>
+        <v>29.1408</v>
       </c>
     </row>
     <row r="43">
@@ -1786,20 +1786,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.9249000000000001</v>
+        <v>0.9059</v>
       </c>
       <c r="F43" t="n">
-        <v>1.5318</v>
+        <v>0.3938</v>
       </c>
       <c r="G43" t="n">
-        <v>15.4552</v>
+        <v>18.1962</v>
       </c>
       <c r="H43" t="n">
-        <v>27.2956</v>
+        <v>29.223</v>
       </c>
     </row>
     <row r="44">
@@ -1822,16 +1822,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.9135</v>
+        <v>0.9046</v>
       </c>
       <c r="F44" t="n">
-        <v>1.5269</v>
+        <v>0.3924</v>
       </c>
       <c r="G44" t="n">
-        <v>16.9971</v>
+        <v>18.1302</v>
       </c>
       <c r="H44" t="n">
-        <v>27.1713</v>
+        <v>29.2557</v>
       </c>
     </row>
     <row r="45">
@@ -1850,20 +1850,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.9078000000000001</v>
+        <v>0.9052</v>
       </c>
       <c r="F45" t="n">
-        <v>1.5352</v>
+        <v>0.3903</v>
       </c>
       <c r="G45" t="n">
-        <v>17.3075</v>
+        <v>17.4082</v>
       </c>
       <c r="H45" t="n">
-        <v>27.3845</v>
+        <v>29.3072</v>
       </c>
     </row>
     <row r="46">
@@ -1882,20 +1882,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.9157</v>
+        <v>0.8717</v>
       </c>
       <c r="F46" t="n">
-        <v>1.5491</v>
+        <v>0.3734</v>
       </c>
       <c r="G46" t="n">
-        <v>16.5345</v>
+        <v>19.8729</v>
       </c>
       <c r="H46" t="n">
-        <v>27.7367</v>
+        <v>29.7093</v>
       </c>
     </row>
     <row r="47">
@@ -1918,16 +1918,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.8887</v>
+        <v>0.8693</v>
       </c>
       <c r="F47" t="n">
-        <v>1.5445</v>
+        <v>0.3799</v>
       </c>
       <c r="G47" t="n">
-        <v>18.4461</v>
+        <v>19.9753</v>
       </c>
       <c r="H47" t="n">
-        <v>27.6215</v>
+        <v>29.5563</v>
       </c>
     </row>
     <row r="48">
@@ -1950,16 +1950,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.9159</v>
+        <v>0.905</v>
       </c>
       <c r="F48" t="n">
-        <v>1.5235</v>
+        <v>0.3993</v>
       </c>
       <c r="G48" t="n">
-        <v>16.8735</v>
+        <v>18.087</v>
       </c>
       <c r="H48" t="n">
-        <v>27.0833</v>
+        <v>29.0907</v>
       </c>
     </row>
     <row r="49">
@@ -1982,16 +1982,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.9305</v>
+        <v>0.9197</v>
       </c>
       <c r="F49" t="n">
-        <v>1.5184</v>
+        <v>0.3989</v>
       </c>
       <c r="G49" t="n">
-        <v>14.9283</v>
+        <v>16.3875</v>
       </c>
       <c r="H49" t="n">
-        <v>26.9496</v>
+        <v>29.1003</v>
       </c>
     </row>
     <row r="50">
@@ -2010,20 +2010,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.9028</v>
+        <v>0.9135</v>
       </c>
       <c r="F50" t="n">
-        <v>1.8172</v>
+        <v>0.1465</v>
       </c>
       <c r="G50" t="n">
-        <v>19.7618</v>
+        <v>18.8213</v>
       </c>
       <c r="H50" t="n">
-        <v>33.8379</v>
+        <v>34.674</v>
       </c>
     </row>
     <row r="51">
@@ -2042,20 +2042,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.8331</v>
+        <v>0.9223</v>
       </c>
       <c r="F51" t="n">
-        <v>1.8561</v>
+        <v>0.1428</v>
       </c>
       <c r="G51" t="n">
-        <v>23.4596</v>
+        <v>17.5734</v>
       </c>
       <c r="H51" t="n">
-        <v>34.634</v>
+        <v>34.7493</v>
       </c>
     </row>
     <row r="52">
@@ -2078,16 +2078,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.8336</v>
+        <v>0.8188</v>
       </c>
       <c r="F52" t="n">
-        <v>1.8501</v>
+        <v>0.1381</v>
       </c>
       <c r="G52" t="n">
-        <v>23.4385</v>
+        <v>24.1079</v>
       </c>
       <c r="H52" t="n">
-        <v>34.5121</v>
+        <v>34.8455</v>
       </c>
     </row>
     <row r="53">
@@ -2106,20 +2106,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.8502999999999999</v>
+        <v>0.8584000000000001</v>
       </c>
       <c r="F53" t="n">
-        <v>1.82</v>
+        <v>0.1336</v>
       </c>
       <c r="G53" t="n">
-        <v>22.7599</v>
+        <v>22.5251</v>
       </c>
       <c r="H53" t="n">
-        <v>33.8948</v>
+        <v>34.9364</v>
       </c>
     </row>
     <row r="54">
@@ -2138,20 +2138,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.8739</v>
+        <v>0.871</v>
       </c>
       <c r="F54" t="n">
-        <v>1.8029</v>
+        <v>0.1649</v>
       </c>
       <c r="G54" t="n">
-        <v>20.7312</v>
+        <v>21.6687</v>
       </c>
       <c r="H54" t="n">
-        <v>33.5407</v>
+        <v>34.2989</v>
       </c>
     </row>
     <row r="55">
@@ -2170,20 +2170,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.8587</v>
+        <v>0.9376</v>
       </c>
       <c r="F55" t="n">
-        <v>1.8448</v>
+        <v>0.1281</v>
       </c>
       <c r="G55" t="n">
-        <v>21.848</v>
+        <v>17.1368</v>
       </c>
       <c r="H55" t="n">
-        <v>34.4035</v>
+        <v>35.0461</v>
       </c>
     </row>
     <row r="56">
@@ -2202,20 +2202,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.9011</v>
+        <v>0.8475</v>
       </c>
       <c r="F56" t="n">
-        <v>1.8064</v>
+        <v>0.1503</v>
       </c>
       <c r="G56" t="n">
-        <v>19.2681</v>
+        <v>23.1077</v>
       </c>
       <c r="H56" t="n">
-        <v>33.6129</v>
+        <v>34.5973</v>
       </c>
     </row>
     <row r="57">
@@ -2234,20 +2234,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.8488</v>
+        <v>0.8532</v>
       </c>
       <c r="F57" t="n">
-        <v>1.8284</v>
+        <v>0.1246</v>
       </c>
       <c r="G57" t="n">
-        <v>22.6746</v>
+        <v>22.5455</v>
       </c>
       <c r="H57" t="n">
-        <v>34.0693</v>
+        <v>35.1174</v>
       </c>
     </row>
     <row r="58">
@@ -2270,16 +2270,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.7772</v>
+        <v>0.7605</v>
       </c>
       <c r="F58" t="n">
-        <v>1.9077</v>
+        <v>0.0189</v>
       </c>
       <c r="G58" t="n">
-        <v>25.173</v>
+        <v>26.0342</v>
       </c>
       <c r="H58" t="n">
-        <v>35.6617</v>
+        <v>37.176</v>
       </c>
     </row>
     <row r="59">
@@ -2302,16 +2302,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.7774</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="F59" t="n">
-        <v>1.9065</v>
+        <v>0.0199</v>
       </c>
       <c r="G59" t="n">
-        <v>25.1655</v>
+        <v>26.0421</v>
       </c>
       <c r="H59" t="n">
-        <v>35.6385</v>
+        <v>37.157</v>
       </c>
     </row>
     <row r="60">
@@ -2334,16 +2334,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.7776</v>
+        <v>0.7611</v>
       </c>
       <c r="F60" t="n">
-        <v>1.9058</v>
+        <v>0.0165</v>
       </c>
       <c r="G60" t="n">
-        <v>25.1502</v>
+        <v>26.0376</v>
       </c>
       <c r="H60" t="n">
-        <v>35.6239</v>
+        <v>37.2224</v>
       </c>
     </row>
     <row r="61">
@@ -2366,16 +2366,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.7786999999999999</v>
+        <v>0.7596000000000001</v>
       </c>
       <c r="F61" t="n">
-        <v>1.9069</v>
+        <v>0.0193</v>
       </c>
       <c r="G61" t="n">
-        <v>25.1075</v>
+        <v>26.0716</v>
       </c>
       <c r="H61" t="n">
-        <v>35.6471</v>
+        <v>37.1693</v>
       </c>
     </row>
     <row r="62">
@@ -2398,16 +2398,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.8122</v>
+        <v>0.8037</v>
       </c>
       <c r="F62" t="n">
-        <v>1.9147</v>
+        <v>0.0546</v>
       </c>
       <c r="G62" t="n">
-        <v>23.9425</v>
+        <v>24.5905</v>
       </c>
       <c r="H62" t="n">
-        <v>35.7992</v>
+        <v>36.494</v>
       </c>
     </row>
     <row r="63">
@@ -2426,20 +2426,20 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.8168</v>
+        <v>0.8536</v>
       </c>
       <c r="F63" t="n">
-        <v>1.9135</v>
+        <v>0.0562</v>
       </c>
       <c r="G63" t="n">
-        <v>23.7081</v>
+        <v>22.4885</v>
       </c>
       <c r="H63" t="n">
-        <v>35.7762</v>
+        <v>36.4632</v>
       </c>
     </row>
     <row r="64">
@@ -2462,16 +2462,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.8649</v>
+        <v>0.8474</v>
       </c>
       <c r="F64" t="n">
-        <v>1.915</v>
+        <v>0.0526</v>
       </c>
       <c r="G64" t="n">
-        <v>21.5597</v>
+        <v>22.4794</v>
       </c>
       <c r="H64" t="n">
-        <v>35.8058</v>
+        <v>36.5323</v>
       </c>
     </row>
     <row r="65">
@@ -2490,20 +2490,20 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.8635</v>
+        <v>0.7987</v>
       </c>
       <c r="F65" t="n">
-        <v>1.9143</v>
+        <v>0.0461</v>
       </c>
       <c r="G65" t="n">
-        <v>21.5804</v>
+        <v>24.7482</v>
       </c>
       <c r="H65" t="n">
-        <v>35.7921</v>
+        <v>36.6578</v>
       </c>
     </row>
     <row r="66">
@@ -2522,20 +2522,20 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.9583</v>
+        <v>0.9159</v>
       </c>
       <c r="F66" t="n">
-        <v>1.8213</v>
+        <v>0.1418</v>
       </c>
       <c r="G66" t="n">
-        <v>14.4913</v>
+        <v>18.776</v>
       </c>
       <c r="H66" t="n">
-        <v>33.9232</v>
+        <v>34.7698</v>
       </c>
     </row>
     <row r="67">
@@ -2554,20 +2554,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.8854</v>
+        <v>0.8303</v>
       </c>
       <c r="F67" t="n">
-        <v>1.8217</v>
+        <v>0.1451</v>
       </c>
       <c r="G67" t="n">
-        <v>20.3074</v>
+        <v>23.5613</v>
       </c>
       <c r="H67" t="n">
-        <v>33.9311</v>
+        <v>34.7028</v>
       </c>
     </row>
     <row r="68">
@@ -2586,20 +2586,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.8645</v>
+        <v>0.833</v>
       </c>
       <c r="F68" t="n">
-        <v>1.8241</v>
+        <v>0.1404</v>
       </c>
       <c r="G68" t="n">
-        <v>21.7712</v>
+        <v>23.4613</v>
       </c>
       <c r="H68" t="n">
-        <v>33.9799</v>
+        <v>34.7978</v>
       </c>
     </row>
     <row r="69">
@@ -2618,20 +2618,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.9429</v>
+        <v>0.9387</v>
       </c>
       <c r="F69" t="n">
-        <v>1.5817</v>
+        <v>0.3366</v>
       </c>
       <c r="G69" t="n">
-        <v>13.8199</v>
+        <v>14.5563</v>
       </c>
       <c r="H69" t="n">
-        <v>28.5488</v>
+        <v>30.5692</v>
       </c>
     </row>
     <row r="70">
@@ -2650,20 +2650,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.9358</v>
+        <v>0.8464</v>
       </c>
       <c r="F70" t="n">
-        <v>1.5979</v>
+        <v>0.3254</v>
       </c>
       <c r="G70" t="n">
-        <v>14.5099</v>
+        <v>20.8689</v>
       </c>
       <c r="H70" t="n">
-        <v>28.9428</v>
+        <v>30.8267</v>
       </c>
     </row>
     <row r="71">
@@ -2682,20 +2682,20 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.9321</v>
+        <v>0.8483000000000001</v>
       </c>
       <c r="F71" t="n">
-        <v>1.5807</v>
+        <v>0.3245</v>
       </c>
       <c r="G71" t="n">
-        <v>15.0314</v>
+        <v>20.8269</v>
       </c>
       <c r="H71" t="n">
-        <v>28.5239</v>
+        <v>30.8479</v>
       </c>
     </row>
     <row r="72">
@@ -2714,20 +2714,20 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.9635</v>
+        <v>0.8486</v>
       </c>
       <c r="F72" t="n">
-        <v>1.5637</v>
+        <v>0.3302</v>
       </c>
       <c r="G72" t="n">
-        <v>11.6482</v>
+        <v>20.7629</v>
       </c>
       <c r="H72" t="n">
-        <v>28.103</v>
+        <v>30.7168</v>
       </c>
     </row>
     <row r="73">
@@ -2746,20 +2746,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.9102</v>
+        <v>0.9028</v>
       </c>
       <c r="F73" t="n">
-        <v>1.5725</v>
+        <v>0.3756</v>
       </c>
       <c r="G73" t="n">
-        <v>16.648</v>
+        <v>17.7567</v>
       </c>
       <c r="H73" t="n">
-        <v>28.3211</v>
+        <v>29.6583</v>
       </c>
     </row>
     <row r="74">
@@ -2782,16 +2782,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.9759</v>
+        <v>0.9717</v>
       </c>
       <c r="F74" t="n">
-        <v>1.5583</v>
+        <v>0.3848</v>
       </c>
       <c r="G74" t="n">
-        <v>10.0006</v>
+        <v>11.0532</v>
       </c>
       <c r="H74" t="n">
-        <v>27.9697</v>
+        <v>29.4384</v>
       </c>
     </row>
     <row r="75">
@@ -2810,20 +2810,20 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.9668</v>
+        <v>0.8925999999999999</v>
       </c>
       <c r="F75" t="n">
-        <v>1.6222</v>
+        <v>0.3036</v>
       </c>
       <c r="G75" t="n">
-        <v>11.2016</v>
+        <v>18.4168</v>
       </c>
       <c r="H75" t="n">
-        <v>29.5253</v>
+        <v>31.3215</v>
       </c>
     </row>
     <row r="76">
@@ -2842,20 +2842,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.9668</v>
+        <v>0.8925999999999999</v>
       </c>
       <c r="F76" t="n">
-        <v>1.6222</v>
+        <v>0.3036</v>
       </c>
       <c r="G76" t="n">
-        <v>11.2016</v>
+        <v>18.4168</v>
       </c>
       <c r="H76" t="n">
-        <v>29.5253</v>
+        <v>31.3215</v>
       </c>
     </row>
     <row r="77">
@@ -2874,20 +2874,20 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.8809</v>
+        <v>0.7827</v>
       </c>
       <c r="F77" t="n">
-        <v>1.8158</v>
+        <v>0.0467</v>
       </c>
       <c r="G77" t="n">
-        <v>19.7791</v>
+        <v>25.1646</v>
       </c>
       <c r="H77" t="n">
-        <v>33.8084</v>
+        <v>36.6455</v>
       </c>
     </row>
     <row r="78">
@@ -2906,20 +2906,20 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.8809</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="F78" t="n">
-        <v>1.815</v>
+        <v>0.0472</v>
       </c>
       <c r="G78" t="n">
-        <v>19.7544</v>
+        <v>25.1718</v>
       </c>
       <c r="H78" t="n">
-        <v>33.7927</v>
+        <v>36.636</v>
       </c>
     </row>
     <row r="79">
@@ -2938,20 +2938,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.8798</v>
+        <v>0.7817</v>
       </c>
       <c r="F79" t="n">
-        <v>1.8244</v>
+        <v>0.0464</v>
       </c>
       <c r="G79" t="n">
-        <v>19.8349</v>
+        <v>25.155</v>
       </c>
       <c r="H79" t="n">
-        <v>33.9858</v>
+        <v>36.6514</v>
       </c>
     </row>
     <row r="80">
@@ -2970,20 +2970,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.8807</v>
+        <v>0.782</v>
       </c>
       <c r="F80" t="n">
-        <v>1.8148</v>
+        <v>0.0474</v>
       </c>
       <c r="G80" t="n">
-        <v>19.7573</v>
+        <v>25.1714</v>
       </c>
       <c r="H80" t="n">
-        <v>33.7878</v>
+        <v>36.6332</v>
       </c>
     </row>
     <row r="81">
@@ -3006,16 +3006,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.8194</v>
+        <v>0.8118</v>
       </c>
       <c r="F81" t="n">
-        <v>1.8907</v>
+        <v>0.0708</v>
       </c>
       <c r="G81" t="n">
-        <v>23.7247</v>
+        <v>24.3684</v>
       </c>
       <c r="H81" t="n">
-        <v>35.3262</v>
+        <v>36.18</v>
       </c>
     </row>
     <row r="82">
@@ -3034,20 +3034,20 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.8403</v>
+        <v>0.8098</v>
       </c>
       <c r="F82" t="n">
-        <v>1.8921</v>
+        <v>0.0641</v>
       </c>
       <c r="G82" t="n">
-        <v>22.7663</v>
+        <v>24.4154</v>
       </c>
       <c r="H82" t="n">
-        <v>35.3547</v>
+        <v>36.3109</v>
       </c>
     </row>
     <row r="83">
@@ -3066,20 +3066,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.9689</v>
+        <v>0.8859</v>
       </c>
       <c r="F83" t="n">
-        <v>1.6235</v>
+        <v>0.3065</v>
       </c>
       <c r="G83" t="n">
-        <v>10.9605</v>
+        <v>18.8019</v>
       </c>
       <c r="H83" t="n">
-        <v>29.5564</v>
+        <v>31.2569</v>
       </c>
     </row>
     <row r="84">
@@ -3098,20 +3098,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.9484</v>
+        <v>0.8873</v>
       </c>
       <c r="F84" t="n">
-        <v>1.6187</v>
+        <v>0.3105</v>
       </c>
       <c r="G84" t="n">
-        <v>13.2014</v>
+        <v>18.7448</v>
       </c>
       <c r="H84" t="n">
-        <v>29.4423</v>
+        <v>31.1655</v>
       </c>
     </row>
     <row r="85">
@@ -3130,20 +3130,20 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.9695</v>
+        <v>0.8854</v>
       </c>
       <c r="F85" t="n">
-        <v>1.6154</v>
+        <v>0.3082</v>
       </c>
       <c r="G85" t="n">
-        <v>10.8963</v>
+        <v>18.8297</v>
       </c>
       <c r="H85" t="n">
-        <v>29.3642</v>
+        <v>31.2181</v>
       </c>
     </row>
     <row r="86">
@@ -3162,20 +3162,20 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.9109</v>
+        <v>0.8711</v>
       </c>
       <c r="F86" t="n">
-        <v>1.5705</v>
+        <v>0.3278</v>
       </c>
       <c r="G86" t="n">
-        <v>16.5022</v>
+        <v>19.7773</v>
       </c>
       <c r="H86" t="n">
-        <v>28.2736</v>
+        <v>30.7734</v>
       </c>
     </row>
     <row r="87">
@@ -3194,20 +3194,20 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.9594</v>
+        <v>0.8521</v>
       </c>
       <c r="F87" t="n">
-        <v>1.5743</v>
+        <v>0.3282</v>
       </c>
       <c r="G87" t="n">
-        <v>11.9686</v>
+        <v>20.8301</v>
       </c>
       <c r="H87" t="n">
-        <v>28.3667</v>
+        <v>30.7632</v>
       </c>
     </row>
     <row r="88">
@@ -3226,20 +3226,20 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.9624</v>
+        <v>0.8514</v>
       </c>
       <c r="F88" t="n">
-        <v>1.5873</v>
+        <v>0.3308</v>
       </c>
       <c r="G88" t="n">
-        <v>11.774</v>
+        <v>20.8297</v>
       </c>
       <c r="H88" t="n">
-        <v>28.6853</v>
+        <v>30.704</v>
       </c>
     </row>
     <row r="89">
@@ -3258,20 +3258,20 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.9417</v>
+        <v>0.8518</v>
       </c>
       <c r="F89" t="n">
-        <v>1.5723</v>
+        <v>0.3502</v>
       </c>
       <c r="G89" t="n">
-        <v>14.0662</v>
+        <v>20.7667</v>
       </c>
       <c r="H89" t="n">
-        <v>28.317</v>
+        <v>30.2563</v>
       </c>
     </row>
     <row r="90">
@@ -3290,20 +3290,20 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.9249000000000001</v>
+        <v>0.9059</v>
       </c>
       <c r="F90" t="n">
-        <v>1.5314</v>
+        <v>0.3937</v>
       </c>
       <c r="G90" t="n">
-        <v>15.4552</v>
+        <v>18.1939</v>
       </c>
       <c r="H90" t="n">
-        <v>27.2859</v>
+        <v>29.2255</v>
       </c>
     </row>
     <row r="91">
@@ -3326,16 +3326,16 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.9135</v>
+        <v>0.9046</v>
       </c>
       <c r="F91" t="n">
-        <v>1.527</v>
+        <v>0.3924</v>
       </c>
       <c r="G91" t="n">
-        <v>16.9973</v>
+        <v>18.1301</v>
       </c>
       <c r="H91" t="n">
-        <v>27.1726</v>
+        <v>29.2558</v>
       </c>
     </row>
     <row r="92">
@@ -3354,20 +3354,20 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.9624</v>
+        <v>0.8514</v>
       </c>
       <c r="F92" t="n">
-        <v>1.5873</v>
+        <v>0.3308</v>
       </c>
       <c r="G92" t="n">
-        <v>11.774</v>
+        <v>20.8297</v>
       </c>
       <c r="H92" t="n">
-        <v>28.6853</v>
+        <v>30.704</v>
       </c>
     </row>
     <row r="93">
@@ -3390,16 +3390,16 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.9135</v>
+        <v>0.9046</v>
       </c>
       <c r="F93" t="n">
-        <v>1.527</v>
+        <v>0.3924</v>
       </c>
       <c r="G93" t="n">
-        <v>16.9973</v>
+        <v>18.1301</v>
       </c>
       <c r="H93" t="n">
-        <v>27.1726</v>
+        <v>29.2558</v>
       </c>
     </row>
     <row r="94">
@@ -3418,20 +3418,20 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9673</v>
       </c>
       <c r="F94" t="n">
-        <v>1.543</v>
+        <v>0.4454</v>
       </c>
       <c r="G94" t="n">
-        <v>14.3543</v>
+        <v>10.976</v>
       </c>
       <c r="H94" t="n">
-        <v>27.5826</v>
+        <v>27.9517</v>
       </c>
     </row>
     <row r="95">
@@ -3454,16 +3454,16 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.7389</v>
+        <v>0.7205</v>
       </c>
       <c r="F95" t="n">
-        <v>2.1663</v>
+        <v>-0.0638</v>
       </c>
       <c r="G95" t="n">
-        <v>28.178</v>
+        <v>29.1931</v>
       </c>
       <c r="H95" t="n">
-        <v>40.4234</v>
+        <v>38.7125</v>
       </c>
     </row>
     <row r="96">
@@ -3482,20 +3482,20 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.967</v>
       </c>
       <c r="F96" t="n">
-        <v>1.555</v>
+        <v>0.447</v>
       </c>
       <c r="G96" t="n">
-        <v>14.2318</v>
+        <v>10.9902</v>
       </c>
       <c r="H96" t="n">
-        <v>27.8863</v>
+        <v>27.9108</v>
       </c>
     </row>
     <row r="97">
@@ -3514,20 +3514,20 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.9387</v>
+        <v>0.9668</v>
       </c>
       <c r="F97" t="n">
-        <v>1.5559</v>
+        <v>0.4476</v>
       </c>
       <c r="G97" t="n">
-        <v>14.2626</v>
+        <v>11.0319</v>
       </c>
       <c r="H97" t="n">
-        <v>27.9092</v>
+        <v>27.8945</v>
       </c>
     </row>
     <row r="98">
@@ -3546,20 +3546,20 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.8999</v>
+        <v>0.8861</v>
       </c>
       <c r="F98" t="n">
-        <v>1.5672</v>
+        <v>0.3663</v>
       </c>
       <c r="G98" t="n">
-        <v>17.4904</v>
+        <v>19.2882</v>
       </c>
       <c r="H98" t="n">
-        <v>28.1908</v>
+        <v>29.8782</v>
       </c>
     </row>
     <row r="99">
@@ -3578,20 +3578,20 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.8667</v>
+        <v>0.8852</v>
       </c>
       <c r="F99" t="n">
-        <v>1.5884</v>
+        <v>0.3613</v>
       </c>
       <c r="G99" t="n">
-        <v>19.8238</v>
+        <v>19.0776</v>
       </c>
       <c r="H99" t="n">
-        <v>28.7123</v>
+        <v>29.9958</v>
       </c>
     </row>
     <row r="100">
@@ -3610,20 +3610,20 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.906</v>
       </c>
       <c r="F100" t="n">
-        <v>1.5808</v>
+        <v>0.3569</v>
       </c>
       <c r="G100" t="n">
-        <v>19.1434</v>
+        <v>17.6027</v>
       </c>
       <c r="H100" t="n">
-        <v>28.5269</v>
+        <v>30.0978</v>
       </c>
     </row>
     <row r="101">
@@ -3642,20 +3642,20 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.877</v>
+        <v>0.8884</v>
       </c>
       <c r="F101" t="n">
-        <v>1.5839</v>
+        <v>0.3565</v>
       </c>
       <c r="G101" t="n">
-        <v>19.1741</v>
+        <v>18.9232</v>
       </c>
       <c r="H101" t="n">
-        <v>28.6031</v>
+        <v>30.109</v>
       </c>
     </row>
     <row r="102">
@@ -3674,20 +3674,20 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.888</v>
+        <v>0.8427</v>
       </c>
       <c r="F102" t="n">
-        <v>1.5781</v>
+        <v>0.3517</v>
       </c>
       <c r="G102" t="n">
-        <v>18.0147</v>
+        <v>21.4074</v>
       </c>
       <c r="H102" t="n">
-        <v>28.4604</v>
+        <v>30.2212</v>
       </c>
     </row>
     <row r="103">
@@ -3706,20 +3706,20 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.9046999999999999</v>
+        <v>0.9395</v>
       </c>
       <c r="F103" t="n">
-        <v>1.5843</v>
+        <v>0.3784</v>
       </c>
       <c r="G103" t="n">
-        <v>17.0032</v>
+        <v>14.6768</v>
       </c>
       <c r="H103" t="n">
-        <v>28.6124</v>
+        <v>29.5917</v>
       </c>
     </row>
     <row r="104">
@@ -3738,20 +3738,20 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.9021</v>
+        <v>0.8851</v>
       </c>
       <c r="F104" t="n">
-        <v>1.5889</v>
+        <v>0.3736</v>
       </c>
       <c r="G104" t="n">
-        <v>17.3864</v>
+        <v>19.2293</v>
       </c>
       <c r="H104" t="n">
-        <v>28.7256</v>
+        <v>29.7066</v>
       </c>
     </row>
     <row r="105">
@@ -3770,20 +3770,20 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.8991</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="F105" t="n">
-        <v>1.5907</v>
+        <v>0.3537</v>
       </c>
       <c r="G105" t="n">
-        <v>17.8042</v>
+        <v>19.3463</v>
       </c>
       <c r="H105" t="n">
-        <v>28.7676</v>
+        <v>30.1744</v>
       </c>
     </row>
     <row r="106">
@@ -3802,20 +3802,20 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.8992</v>
+        <v>0.9366</v>
       </c>
       <c r="F106" t="n">
-        <v>1.5784</v>
+        <v>0.3557</v>
       </c>
       <c r="G106" t="n">
-        <v>17.7693</v>
+        <v>15.1275</v>
       </c>
       <c r="H106" t="n">
-        <v>28.4683</v>
+        <v>30.1262</v>
       </c>
     </row>
     <row r="107">
@@ -3834,20 +3834,20 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.8659</v>
+        <v>0.9348</v>
       </c>
       <c r="F107" t="n">
-        <v>1.5852</v>
+        <v>0.3515</v>
       </c>
       <c r="G107" t="n">
-        <v>19.8296</v>
+        <v>15.3734</v>
       </c>
       <c r="H107" t="n">
-        <v>28.6347</v>
+        <v>30.2255</v>
       </c>
     </row>
     <row r="108">
@@ -3866,20 +3866,20 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.968</v>
+        <v>0.9532</v>
       </c>
       <c r="F108" t="n">
-        <v>1.5391</v>
+        <v>0.3813</v>
       </c>
       <c r="G108" t="n">
-        <v>11.1535</v>
+        <v>13.7582</v>
       </c>
       <c r="H108" t="n">
-        <v>27.4825</v>
+        <v>29.5219</v>
       </c>
     </row>
     <row r="109">
@@ -3898,20 +3898,20 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.9363</v>
+        <v>0.951</v>
       </c>
       <c r="F109" t="n">
-        <v>1.5516</v>
+        <v>0.37</v>
       </c>
       <c r="G109" t="n">
-        <v>14.2119</v>
+        <v>14.4107</v>
       </c>
       <c r="H109" t="n">
-        <v>27.7995</v>
+        <v>29.7916</v>
       </c>
     </row>
     <row r="110">
@@ -3930,20 +3930,20 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.9096</v>
+        <v>0.8753</v>
       </c>
       <c r="F110" t="n">
-        <v>1.5962</v>
+        <v>0.3582</v>
       </c>
       <c r="G110" t="n">
-        <v>16.7902</v>
+        <v>20.0758</v>
       </c>
       <c r="H110" t="n">
-        <v>28.9028</v>
+        <v>30.0684</v>
       </c>
     </row>
     <row r="111">
@@ -3962,20 +3962,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.95</v>
+        <v>0.8635</v>
       </c>
       <c r="F111" t="n">
-        <v>1.612</v>
+        <v>0.3555</v>
       </c>
       <c r="G111" t="n">
-        <v>13.6294</v>
+        <v>20.5024</v>
       </c>
       <c r="H111" t="n">
-        <v>29.2827</v>
+        <v>30.1327</v>
       </c>
     </row>
     <row r="112">
@@ -3994,20 +3994,20 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="F112" t="n">
-        <v>1.5434</v>
+        <v>0.3825</v>
       </c>
       <c r="G112" t="n">
-        <v>11.3432</v>
+        <v>11.2923</v>
       </c>
       <c r="H112" t="n">
-        <v>27.5929</v>
+        <v>29.4941</v>
       </c>
     </row>
     <row r="113">
@@ -4026,20 +4026,20 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.9362</v>
+        <v>0.9515</v>
       </c>
       <c r="F113" t="n">
-        <v>1.5514</v>
+        <v>0.379</v>
       </c>
       <c r="G113" t="n">
-        <v>14.2186</v>
+        <v>14.4395</v>
       </c>
       <c r="H113" t="n">
-        <v>27.7953</v>
+        <v>29.5773</v>
       </c>
     </row>
     <row r="114">
@@ -4058,20 +4058,20 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.9106</v>
+        <v>0.8761</v>
       </c>
       <c r="F114" t="n">
-        <v>1.5977</v>
+        <v>0.3601</v>
       </c>
       <c r="G114" t="n">
-        <v>16.6984</v>
+        <v>20.0713</v>
       </c>
       <c r="H114" t="n">
-        <v>28.9398</v>
+        <v>30.025</v>
       </c>
     </row>
     <row r="115">
@@ -4090,20 +4090,20 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.9492</v>
+        <v>0.8484</v>
       </c>
       <c r="F115" t="n">
-        <v>1.614</v>
+        <v>0.3454</v>
       </c>
       <c r="G115" t="n">
-        <v>13.7047</v>
+        <v>21.3664</v>
       </c>
       <c r="H115" t="n">
-        <v>29.3299</v>
+        <v>30.3674</v>
       </c>
     </row>
     <row r="116">
@@ -4126,16 +4126,16 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.8047</v>
+        <v>0.7901</v>
       </c>
       <c r="F116" t="n">
-        <v>1.9023</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="G116" t="n">
-        <v>24.3067</v>
+        <v>25.3233</v>
       </c>
       <c r="H116" t="n">
-        <v>35.5565</v>
+        <v>35.8429</v>
       </c>
     </row>
     <row r="117">
@@ -4158,16 +4158,16 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.7993</v>
+        <v>0.7863</v>
       </c>
       <c r="F117" t="n">
-        <v>1.8943</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="G117" t="n">
-        <v>24.4299</v>
+        <v>25.4837</v>
       </c>
       <c r="H117" t="n">
-        <v>35.3984</v>
+        <v>35.8356</v>
       </c>
     </row>
     <row r="118">
@@ -4186,20 +4186,20 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.8991</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="F118" t="n">
-        <v>1.5907</v>
+        <v>0.3537</v>
       </c>
       <c r="G118" t="n">
-        <v>17.8042</v>
+        <v>19.3463</v>
       </c>
       <c r="H118" t="n">
-        <v>28.7676</v>
+        <v>30.1744</v>
       </c>
     </row>
     <row r="119">
@@ -4218,20 +4218,20 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.9362</v>
+        <v>0.9515</v>
       </c>
       <c r="F119" t="n">
-        <v>1.5514</v>
+        <v>0.379</v>
       </c>
       <c r="G119" t="n">
-        <v>14.2186</v>
+        <v>14.4395</v>
       </c>
       <c r="H119" t="n">
-        <v>27.7953</v>
+        <v>29.5773</v>
       </c>
     </row>
     <row r="120">
@@ -4250,20 +4250,20 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.8763</v>
+        <v>0.8159</v>
       </c>
       <c r="F120" t="n">
-        <v>1.6378</v>
+        <v>0.3056</v>
       </c>
       <c r="G120" t="n">
-        <v>18.935</v>
+        <v>22.468</v>
       </c>
       <c r="H120" t="n">
-        <v>29.8948</v>
+        <v>31.276</v>
       </c>
     </row>
     <row r="121">
@@ -4282,20 +4282,20 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.8763</v>
+        <v>0.8159</v>
       </c>
       <c r="F121" t="n">
-        <v>1.6378</v>
+        <v>0.3056</v>
       </c>
       <c r="G121" t="n">
-        <v>18.935</v>
+        <v>22.468</v>
       </c>
       <c r="H121" t="n">
-        <v>29.8948</v>
+        <v>31.276</v>
       </c>
     </row>
     <row r="122">
@@ -4314,20 +4314,20 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.8799</v>
+        <v>0.9069</v>
       </c>
       <c r="F122" t="n">
-        <v>1.6218</v>
+        <v>0.3519</v>
       </c>
       <c r="G122" t="n">
-        <v>18.5949</v>
+        <v>17.0815</v>
       </c>
       <c r="H122" t="n">
-        <v>29.5168</v>
+        <v>30.2159</v>
       </c>
     </row>
     <row r="123">
@@ -4346,20 +4346,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.9362</v>
+        <v>0.9515</v>
       </c>
       <c r="F123" t="n">
-        <v>1.5511</v>
+        <v>0.3774</v>
       </c>
       <c r="G123" t="n">
-        <v>14.2189</v>
+        <v>14.4271</v>
       </c>
       <c r="H123" t="n">
-        <v>27.7886</v>
+        <v>29.6145</v>
       </c>
     </row>
     <row r="124">
@@ -4378,20 +4378,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.9509</v>
+        <v>0.9315</v>
       </c>
       <c r="F124" t="n">
-        <v>1.5695</v>
+        <v>0.3771</v>
       </c>
       <c r="G124" t="n">
-        <v>12.9682</v>
+        <v>15.2658</v>
       </c>
       <c r="H124" t="n">
-        <v>28.2467</v>
+        <v>29.6225</v>
       </c>
     </row>
     <row r="125">
@@ -4410,20 +4410,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.9426</v>
+        <v>0.9649</v>
       </c>
       <c r="F125" t="n">
-        <v>1.552</v>
+        <v>0.4483</v>
       </c>
       <c r="G125" t="n">
-        <v>13.9818</v>
+        <v>11.2804</v>
       </c>
       <c r="H125" t="n">
-        <v>27.811</v>
+        <v>27.8773</v>
       </c>
     </row>
     <row r="126">
@@ -4442,20 +4442,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.8944</v>
+        <v>0.8576</v>
       </c>
       <c r="F126" t="n">
-        <v>1.6104</v>
+        <v>0.3317</v>
       </c>
       <c r="G126" t="n">
-        <v>17.6916</v>
+        <v>20.1353</v>
       </c>
       <c r="H126" t="n">
-        <v>29.2445</v>
+        <v>30.6829</v>
       </c>
     </row>
     <row r="127">
@@ -4478,16 +4478,16 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.7743</v>
+        <v>0.7564</v>
       </c>
       <c r="F127" t="n">
-        <v>1.9489</v>
+        <v>0.0329</v>
       </c>
       <c r="G127" t="n">
-        <v>25.2565</v>
+        <v>26.1988</v>
       </c>
       <c r="H127" t="n">
-        <v>36.4627</v>
+        <v>36.9112</v>
       </c>
     </row>
     <row r="128">
@@ -4506,20 +4506,20 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.8963</v>
+        <v>0.8605</v>
       </c>
       <c r="F128" t="n">
-        <v>1.6034</v>
+        <v>0.3292</v>
       </c>
       <c r="G128" t="n">
-        <v>17.5701</v>
+        <v>19.9125</v>
       </c>
       <c r="H128" t="n">
-        <v>29.0767</v>
+        <v>30.7411</v>
       </c>
     </row>
     <row r="129">
@@ -4538,20 +4538,20 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.8988</v>
+        <v>0.8613</v>
       </c>
       <c r="F129" t="n">
-        <v>1.6063</v>
+        <v>0.3313</v>
       </c>
       <c r="G129" t="n">
-        <v>17.3501</v>
+        <v>19.8563</v>
       </c>
       <c r="H129" t="n">
-        <v>29.1456</v>
+        <v>30.6921</v>
       </c>
     </row>
     <row r="130">
@@ -4570,20 +4570,20 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.8975</v>
+        <v>0.8598</v>
       </c>
       <c r="F130" t="n">
-        <v>1.609</v>
+        <v>0.3303</v>
       </c>
       <c r="G130" t="n">
-        <v>17.4129</v>
+        <v>19.9376</v>
       </c>
       <c r="H130" t="n">
-        <v>29.2118</v>
+        <v>30.7152</v>
       </c>
     </row>
     <row r="131">
@@ -4602,20 +4602,20 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="F131" t="n">
-        <v>1.6082</v>
+        <v>0.3337</v>
       </c>
       <c r="G131" t="n">
-        <v>17.4673</v>
+        <v>19.8571</v>
       </c>
       <c r="H131" t="n">
-        <v>29.1929</v>
+        <v>30.6363</v>
       </c>
     </row>
     <row r="132">
@@ -4638,16 +4638,16 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.8978</v>
+        <v>0.8608</v>
       </c>
       <c r="F132" t="n">
-        <v>1.6035</v>
+        <v>0.3217</v>
       </c>
       <c r="G132" t="n">
-        <v>17.5596</v>
+        <v>19.9175</v>
       </c>
       <c r="H132" t="n">
-        <v>29.0798</v>
+        <v>30.9113</v>
       </c>
     </row>
     <row r="133">
@@ -4670,16 +4670,16 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.8938</v>
+        <v>0.863</v>
       </c>
       <c r="F133" t="n">
-        <v>1.6025</v>
+        <v>0.3236</v>
       </c>
       <c r="G133" t="n">
-        <v>17.8195</v>
+        <v>19.8332</v>
       </c>
       <c r="H133" t="n">
-        <v>29.0544</v>
+        <v>30.8674</v>
       </c>
     </row>
     <row r="134">
@@ -4698,20 +4698,20 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.8967000000000001</v>
+        <v>0.8627</v>
       </c>
       <c r="F134" t="n">
-        <v>1.6034</v>
+        <v>0.3299</v>
       </c>
       <c r="G134" t="n">
-        <v>17.635</v>
+        <v>19.8095</v>
       </c>
       <c r="H134" t="n">
-        <v>29.0754</v>
+        <v>30.7246</v>
       </c>
     </row>
     <row r="135">
@@ -4730,20 +4730,20 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0.8966</v>
+        <v>0.8608</v>
       </c>
       <c r="F135" t="n">
-        <v>1.6039</v>
+        <v>0.3287</v>
       </c>
       <c r="G135" t="n">
-        <v>17.6013</v>
+        <v>19.8909</v>
       </c>
       <c r="H135" t="n">
-        <v>29.0892</v>
+        <v>30.7522</v>
       </c>
     </row>
     <row r="136">
@@ -4762,20 +4762,20 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.8974</v>
+        <v>0.8622</v>
       </c>
       <c r="F136" t="n">
-        <v>1.6061</v>
+        <v>0.3318</v>
       </c>
       <c r="G136" t="n">
-        <v>17.51</v>
+        <v>19.822</v>
       </c>
       <c r="H136" t="n">
-        <v>29.1405</v>
+        <v>30.6808</v>
       </c>
     </row>
     <row r="137">
@@ -4794,20 +4794,20 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.9762999999999999</v>
+        <v>0.8939</v>
       </c>
       <c r="F137" t="n">
-        <v>1.5516</v>
+        <v>0.3574</v>
       </c>
       <c r="G137" t="n">
-        <v>9.8649</v>
+        <v>18.2109</v>
       </c>
       <c r="H137" t="n">
-        <v>27.8003</v>
+        <v>30.0875</v>
       </c>
     </row>
     <row r="138">
@@ -4826,20 +4826,20 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.9741</v>
+        <v>0.8615</v>
       </c>
       <c r="F138" t="n">
-        <v>1.5606</v>
+        <v>0.3489</v>
       </c>
       <c r="G138" t="n">
-        <v>10.3361</v>
+        <v>20.1894</v>
       </c>
       <c r="H138" t="n">
-        <v>28.026</v>
+        <v>30.2855</v>
       </c>
     </row>
     <row r="139">
@@ -4858,20 +4858,20 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.9768</v>
+        <v>0.8603</v>
       </c>
       <c r="F139" t="n">
-        <v>1.5622</v>
+        <v>0.358</v>
       </c>
       <c r="G139" t="n">
-        <v>9.9085</v>
+        <v>20.166</v>
       </c>
       <c r="H139" t="n">
-        <v>28.0653</v>
+        <v>30.073</v>
       </c>
     </row>
     <row r="140">
@@ -4890,20 +4890,20 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.9705</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="F140" t="n">
-        <v>1.5291</v>
+        <v>0.3875</v>
       </c>
       <c r="G140" t="n">
-        <v>10.5632</v>
+        <v>15.0484</v>
       </c>
       <c r="H140" t="n">
-        <v>27.2274</v>
+        <v>29.373</v>
       </c>
     </row>
     <row r="141">
@@ -4922,20 +4922,20 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.9464</v>
+        <v>0.9363</v>
       </c>
       <c r="F141" t="n">
-        <v>1.5071</v>
+        <v>0.4506</v>
       </c>
       <c r="G141" t="n">
-        <v>13.2282</v>
+        <v>14.614</v>
       </c>
       <c r="H141" t="n">
-        <v>26.6563</v>
+        <v>27.8201</v>
       </c>
     </row>
     <row r="142">
@@ -4954,20 +4954,20 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.9741</v>
+        <v>0.8615</v>
       </c>
       <c r="F142" t="n">
-        <v>1.5606</v>
+        <v>0.3489</v>
       </c>
       <c r="G142" t="n">
-        <v>10.3361</v>
+        <v>20.1894</v>
       </c>
       <c r="H142" t="n">
-        <v>28.026</v>
+        <v>30.2855</v>
       </c>
     </row>
     <row r="143">
@@ -4986,20 +4986,20 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.9491000000000001</v>
+        <v>0.8581</v>
       </c>
       <c r="F143" t="n">
-        <v>1.5626</v>
+        <v>0.358</v>
       </c>
       <c r="G143" t="n">
-        <v>13.1549</v>
+        <v>20.2292</v>
       </c>
       <c r="H143" t="n">
-        <v>28.0755</v>
+        <v>30.0736</v>
       </c>
     </row>
     <row r="144">
@@ -5018,20 +5018,20 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.9512</v>
+        <v>0.8581</v>
       </c>
       <c r="F144" t="n">
-        <v>1.5541</v>
+        <v>0.3572</v>
       </c>
       <c r="G144" t="n">
-        <v>12.9847</v>
+        <v>20.2402</v>
       </c>
       <c r="H144" t="n">
-        <v>27.8628</v>
+        <v>30.0911</v>
       </c>
     </row>
     <row r="145">
@@ -5050,20 +5050,20 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0.9464</v>
+        <v>0.9363</v>
       </c>
       <c r="F145" t="n">
-        <v>1.5071</v>
+        <v>0.4506</v>
       </c>
       <c r="G145" t="n">
-        <v>13.2282</v>
+        <v>14.614</v>
       </c>
       <c r="H145" t="n">
-        <v>26.6563</v>
+        <v>27.8201</v>
       </c>
     </row>
     <row r="146">
@@ -5086,16 +5086,16 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.7722</v>
+        <v>0.756</v>
       </c>
       <c r="F146" t="n">
-        <v>1.9523</v>
+        <v>0.0335</v>
       </c>
       <c r="G146" t="n">
-        <v>25.3268</v>
+        <v>26.1989</v>
       </c>
       <c r="H146" t="n">
-        <v>36.5276</v>
+        <v>36.8979</v>
       </c>
     </row>
     <row r="147">
@@ -5118,16 +5118,16 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.7745</v>
+        <v>0.7597</v>
       </c>
       <c r="F147" t="n">
-        <v>1.9478</v>
+        <v>0.0366</v>
       </c>
       <c r="G147" t="n">
-        <v>25.2433</v>
+        <v>26.0472</v>
       </c>
       <c r="H147" t="n">
-        <v>36.441</v>
+        <v>36.8404</v>
       </c>
     </row>
     <row r="148">
@@ -5150,16 +5150,16 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.775</v>
+        <v>0.7623</v>
       </c>
       <c r="F148" t="n">
-        <v>1.9463</v>
+        <v>0.0397</v>
       </c>
       <c r="G148" t="n">
-        <v>25.2343</v>
+        <v>25.9947</v>
       </c>
       <c r="H148" t="n">
-        <v>36.413</v>
+        <v>36.7796</v>
       </c>
     </row>
     <row r="149">
@@ -5182,16 +5182,16 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.7721</v>
+        <v>0.7572</v>
       </c>
       <c r="F149" t="n">
-        <v>1.9445</v>
+        <v>0.0382</v>
       </c>
       <c r="G149" t="n">
-        <v>25.2989</v>
+        <v>26.1233</v>
       </c>
       <c r="H149" t="n">
-        <v>36.3784</v>
+        <v>36.8085</v>
       </c>
     </row>
     <row r="150">
@@ -5214,16 +5214,16 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.7735</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="F150" t="n">
-        <v>1.9514</v>
+        <v>0.0351</v>
       </c>
       <c r="G150" t="n">
-        <v>25.2923</v>
+        <v>26.2139</v>
       </c>
       <c r="H150" t="n">
-        <v>36.5112</v>
+        <v>36.8677</v>
       </c>
     </row>
     <row r="151">
@@ -5246,16 +5246,16 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.773</v>
+        <v>0.7554</v>
       </c>
       <c r="F151" t="n">
-        <v>1.9506</v>
+        <v>0.0357</v>
       </c>
       <c r="G151" t="n">
-        <v>25.2993</v>
+        <v>26.2263</v>
       </c>
       <c r="H151" t="n">
-        <v>36.4953</v>
+        <v>36.8572</v>
       </c>
     </row>
     <row r="152">
@@ -5278,16 +5278,16 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0.7733</v>
+        <v>0.7554</v>
       </c>
       <c r="F152" t="n">
-        <v>1.9512</v>
+        <v>0.0358</v>
       </c>
       <c r="G152" t="n">
-        <v>25.2813</v>
+        <v>26.2139</v>
       </c>
       <c r="H152" t="n">
-        <v>36.5065</v>
+        <v>36.854</v>
       </c>
     </row>
     <row r="153">
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>0.7724</v>
+        <v>0.7565</v>
       </c>
       <c r="F153" t="n">
-        <v>1.9534</v>
+        <v>0.0329</v>
       </c>
       <c r="G153" t="n">
-        <v>25.3141</v>
+        <v>26.1781</v>
       </c>
       <c r="H153" t="n">
-        <v>36.549</v>
+        <v>36.9108</v>
       </c>
     </row>
     <row r="154">
@@ -5342,16 +5342,16 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.7741</v>
+        <v>0.7564</v>
       </c>
       <c r="F154" t="n">
-        <v>1.9499</v>
+        <v>0.0364</v>
       </c>
       <c r="G154" t="n">
-        <v>25.2409</v>
+        <v>26.1824</v>
       </c>
       <c r="H154" t="n">
-        <v>36.4824</v>
+        <v>36.8436</v>
       </c>
     </row>
     <row r="155">
@@ -5374,16 +5374,16 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.8138</v>
+        <v>0.7995</v>
       </c>
       <c r="F155" t="n">
-        <v>1.9272</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="G155" t="n">
-        <v>23.8183</v>
+        <v>24.7203</v>
       </c>
       <c r="H155" t="n">
-        <v>36.0436</v>
+        <v>36.2687</v>
       </c>
     </row>
     <row r="156">
@@ -5406,16 +5406,16 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.8103</v>
+        <v>0.798</v>
       </c>
       <c r="F156" t="n">
-        <v>1.9226</v>
+        <v>0.0527</v>
       </c>
       <c r="G156" t="n">
-        <v>23.9384</v>
+        <v>24.7785</v>
       </c>
       <c r="H156" t="n">
-        <v>35.9535</v>
+        <v>36.5313</v>
       </c>
     </row>
     <row r="157">
@@ -5438,16 +5438,16 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.8121</v>
+        <v>0.7991</v>
       </c>
       <c r="F157" t="n">
-        <v>1.9155</v>
+        <v>0.0572</v>
       </c>
       <c r="G157" t="n">
-        <v>23.8847</v>
+        <v>24.7505</v>
       </c>
       <c r="H157" t="n">
-        <v>35.8143</v>
+        <v>36.443</v>
       </c>
     </row>
     <row r="158">
@@ -5470,16 +5470,16 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.8241000000000001</v>
+        <v>0.8131</v>
       </c>
       <c r="F158" t="n">
-        <v>1.8929</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="G158" t="n">
-        <v>23.9114</v>
+        <v>24.5314</v>
       </c>
       <c r="H158" t="n">
-        <v>35.3704</v>
+        <v>35.7976</v>
       </c>
     </row>
     <row r="159">
@@ -5498,20 +5498,20 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.8939</v>
+        <v>0.8973</v>
       </c>
       <c r="F159" t="n">
-        <v>1.5849</v>
+        <v>0.3677</v>
       </c>
       <c r="G159" t="n">
-        <v>17.4346</v>
+        <v>17.7805</v>
       </c>
       <c r="H159" t="n">
-        <v>28.626</v>
+        <v>29.8444</v>
       </c>
     </row>
     <row r="160">
@@ -5534,16 +5534,16 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.7875</v>
+        <v>0.7812</v>
       </c>
       <c r="F160" t="n">
-        <v>1.9047</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="G160" t="n">
-        <v>24.7046</v>
+        <v>25.4625</v>
       </c>
       <c r="H160" t="n">
-        <v>35.6036</v>
+        <v>36.2244</v>
       </c>
     </row>
     <row r="161">
@@ -5566,16 +5566,16 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>0.7885</v>
+        <v>0.7805</v>
       </c>
       <c r="F161" t="n">
-        <v>1.9061</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="G161" t="n">
-        <v>24.6798</v>
+        <v>25.5384</v>
       </c>
       <c r="H161" t="n">
-        <v>35.6305</v>
+        <v>36.2131</v>
       </c>
     </row>
     <row r="162">
@@ -5594,20 +5594,20 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>0.892</v>
+        <v>0.9103</v>
       </c>
       <c r="F162" t="n">
-        <v>1.5897</v>
+        <v>0.3656</v>
       </c>
       <c r="G162" t="n">
-        <v>17.8023</v>
+        <v>16.7321</v>
       </c>
       <c r="H162" t="n">
-        <v>28.7434</v>
+        <v>29.8938</v>
       </c>
     </row>
     <row r="163">
@@ -5626,20 +5626,20 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.9545</v>
+        <v>0.8539</v>
       </c>
       <c r="F163" t="n">
-        <v>1.5997</v>
+        <v>0.329</v>
       </c>
       <c r="G163" t="n">
-        <v>12.4195</v>
+        <v>20.6441</v>
       </c>
       <c r="H163" t="n">
-        <v>28.9869</v>
+        <v>30.7451</v>
       </c>
     </row>
     <row r="164">
@@ -5658,20 +5658,20 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>0.9706</v>
+        <v>0.9338</v>
       </c>
       <c r="F164" t="n">
-        <v>1.5285</v>
+        <v>0.3876</v>
       </c>
       <c r="G164" t="n">
-        <v>10.5569</v>
+        <v>15.0619</v>
       </c>
       <c r="H164" t="n">
-        <v>27.2124</v>
+        <v>29.3724</v>
       </c>
     </row>
     <row r="165">
@@ -5690,20 +5690,20 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.9426</v>
+        <v>0.9649</v>
       </c>
       <c r="F165" t="n">
-        <v>1.552</v>
+        <v>0.4483</v>
       </c>
       <c r="G165" t="n">
-        <v>13.9818</v>
+        <v>11.2804</v>
       </c>
       <c r="H165" t="n">
-        <v>27.811</v>
+        <v>27.8773</v>
       </c>
     </row>
     <row r="166">
@@ -5722,20 +5722,20 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.7506</v>
+        <v>0.7239</v>
       </c>
       <c r="F166" t="n">
-        <v>2.1677</v>
+        <v>-0.06</v>
       </c>
       <c r="G166" t="n">
-        <v>27.6902</v>
+        <v>29.1147</v>
       </c>
       <c r="H166" t="n">
-        <v>40.4488</v>
+        <v>38.6423</v>
       </c>
     </row>
     <row r="167">
@@ -5758,16 +5758,16 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0.882</v>
+        <v>0.8592</v>
       </c>
       <c r="F167" t="n">
-        <v>1.5414</v>
+        <v>0.3636</v>
       </c>
       <c r="G167" t="n">
-        <v>18.5199</v>
+        <v>20.0673</v>
       </c>
       <c r="H167" t="n">
-        <v>27.5427</v>
+        <v>29.9409</v>
       </c>
     </row>
     <row r="168">
@@ -5786,20 +5786,20 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0.9225</v>
+        <v>0.8838</v>
       </c>
       <c r="F168" t="n">
-        <v>1.5409</v>
+        <v>0.3907</v>
       </c>
       <c r="G168" t="n">
-        <v>15.7474</v>
+        <v>19.3591</v>
       </c>
       <c r="H168" t="n">
-        <v>27.5304</v>
+        <v>29.2984</v>
       </c>
     </row>
     <row r="169">
@@ -5818,20 +5818,20 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.9479</v>
+        <v>0.9078000000000001</v>
       </c>
       <c r="F169" t="n">
-        <v>1.5467</v>
+        <v>0.3438</v>
       </c>
       <c r="G169" t="n">
-        <v>13.8074</v>
+        <v>17.1038</v>
       </c>
       <c r="H169" t="n">
-        <v>27.6769</v>
+        <v>30.405</v>
       </c>
     </row>
     <row r="170">
@@ -5850,20 +5850,20 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>0.9204</v>
+        <v>0.9527</v>
       </c>
       <c r="F170" t="n">
-        <v>1.5972</v>
+        <v>0.364</v>
       </c>
       <c r="G170" t="n">
-        <v>16.2539</v>
+        <v>13.7931</v>
       </c>
       <c r="H170" t="n">
-        <v>28.9269</v>
+        <v>29.9317</v>
       </c>
     </row>
     <row r="171">
@@ -5882,20 +5882,20 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>0.9704</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="F171" t="n">
-        <v>1.5146</v>
+        <v>0.43</v>
       </c>
       <c r="G171" t="n">
-        <v>10.494</v>
+        <v>11.462</v>
       </c>
       <c r="H171" t="n">
-        <v>26.8505</v>
+        <v>28.336</v>
       </c>
     </row>
     <row r="172">
@@ -5914,20 +5914,20 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>0.9215</v>
+        <v>0.9183</v>
       </c>
       <c r="F172" t="n">
-        <v>1.5806</v>
+        <v>0.3444</v>
       </c>
       <c r="G172" t="n">
-        <v>15.3925</v>
+        <v>16.4656</v>
       </c>
       <c r="H172" t="n">
-        <v>28.5216</v>
+        <v>30.3907</v>
       </c>
     </row>
   </sheetData>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/X13.cis.beta.carotene/RANDOMSEARCH_DETAILS_X13.cis.beta.carotene.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/X13.cis.beta.carotene/RANDOMSEARCH_DETAILS_X13.cis.beta.carotene.xlsx
@@ -474,7 +474,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E2" t="n">
